--- a/Top100 Companies Analysis (1).xlsx
+++ b/Top100 Companies Analysis (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FRIDAY\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FCE21F2-4319-4665-B1AB-CBFA0DD8F02A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB5BC496-DC77-4227-9F0F-CD52E908C0DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="6" xr2:uid="{819FB59D-85F3-4B90-A64F-570EC18FD9B6}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Analysis of PivotTables&amp;Charts" sheetId="4" r:id="rId1"/>
     <sheet name="KPI_Data" sheetId="6" r:id="rId2"/>
     <sheet name="Cleaned Data Top95" sheetId="3" r:id="rId3"/>
-    <sheet name="Raw data top95" sheetId="1" r:id="rId4"/>
+    <sheet name="Raw data Top100" sheetId="1" r:id="rId4"/>
     <sheet name="PDF Report" sheetId="10" r:id="rId5"/>
     <sheet name="Project Report" sheetId="8" r:id="rId6"/>
     <sheet name="Dashboard" sheetId="5" r:id="rId7"/>
@@ -17964,7 +17964,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AA9A1832-5041-4620-92BD-1042BB7B8FAE}" name="Table_15" displayName="Table_15" ref="A1:T96" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:T96" xr:uid="{AA9A1832-5041-4620-92BD-1042BB7B8FAE}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T96">
-    <sortCondition descending="1" ref="P1:P96"/>
+    <sortCondition descending="1" ref="N1:N96"/>
   </sortState>
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{95410657-C774-475F-8C73-1122E3A570DF}" uniqueName="1" name="Rank" queryTableFieldId="1"/>
@@ -18389,11 +18389,11 @@
       </c>
       <c r="C3" s="14">
         <f>SUM('Cleaned Data Top95'!O:O)</f>
-        <v>11373.638999999997</v>
+        <v>11373.639000000006</v>
       </c>
       <c r="D3" s="15">
         <f>AVERAGE('Cleaned Data Top95'!P:P)</f>
-        <v>27.681578947368426</v>
+        <v>27.681578947368415</v>
       </c>
       <c r="E3" s="16">
         <f>SUM(Table_15[Employees])</f>
@@ -19145,58 +19145,58 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>129</v>
+        <v>33</v>
       </c>
       <c r="C3" t="s">
-        <v>130</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s">
         <v>26</v>
       </c>
       <c r="H3" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="I3" t="s">
-        <v>101</v>
+        <v>28</v>
       </c>
       <c r="J3">
-        <v>1983</v>
+        <v>1976</v>
       </c>
       <c r="K3">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>166000</v>
       </c>
       <c r="M3">
-        <v>868.67</v>
+        <v>4609</v>
       </c>
       <c r="N3">
-        <v>0.86866999999999994</v>
+        <v>4.609</v>
       </c>
       <c r="O3">
-        <v>91.71</v>
+        <v>451.44</v>
       </c>
       <c r="P3">
-        <v>70.87</v>
+        <v>31.89</v>
       </c>
       <c r="Q3" s="10">
         <v>46265</v>
       </c>
       <c r="R3" t="s">
-        <v>133</v>
+        <v>37</v>
       </c>
       <c r="S3" t="s">
         <v>30</v>
@@ -19207,58 +19207,58 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4">
-        <v>71</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>439</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>440</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>441</v>
+        <v>41</v>
       </c>
       <c r="E4" t="s">
-        <v>172</v>
+        <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="G4" t="s">
-        <v>236</v>
+        <v>26</v>
       </c>
       <c r="H4" t="s">
-        <v>442</v>
+        <v>36</v>
       </c>
       <c r="I4" t="s">
-        <v>173</v>
+        <v>28</v>
       </c>
       <c r="J4">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="K4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>190820</v>
       </c>
       <c r="M4">
-        <v>242.18</v>
+        <v>4096</v>
       </c>
       <c r="N4">
-        <v>0.24218000000000001</v>
+        <v>4.0960000000000001</v>
       </c>
       <c r="O4">
-        <v>26.44</v>
+        <v>422.49</v>
       </c>
       <c r="P4">
-        <v>67.239999999999995</v>
+        <v>46.31</v>
       </c>
       <c r="Q4" s="10">
         <v>46265</v>
       </c>
       <c r="R4" t="s">
-        <v>443</v>
+        <v>42</v>
       </c>
       <c r="S4" t="s">
         <v>30</v>
@@ -19269,16 +19269,16 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>146</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
-        <v>147</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>148</v>
+        <v>46</v>
       </c>
       <c r="E5" t="s">
         <v>24</v>
@@ -19287,40 +19287,40 @@
         <v>25</v>
       </c>
       <c r="G5" t="s">
-        <v>107</v>
+        <v>26</v>
       </c>
       <c r="H5" t="s">
-        <v>149</v>
+        <v>36</v>
       </c>
       <c r="I5" t="s">
-        <v>109</v>
+        <v>28</v>
       </c>
       <c r="J5">
-        <v>1958</v>
+        <v>1975</v>
       </c>
       <c r="K5">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="L5">
-        <v>34100</v>
+        <v>223000</v>
       </c>
       <c r="M5">
-        <v>709.08</v>
+        <v>3783</v>
       </c>
       <c r="N5">
-        <v>0.70908000000000004</v>
+        <v>3.7829999999999999</v>
       </c>
       <c r="O5">
-        <v>43.02</v>
+        <v>318.27</v>
       </c>
       <c r="P5">
-        <v>61.480000000000004</v>
+        <v>48.54</v>
       </c>
       <c r="Q5" s="10">
         <v>46265</v>
       </c>
       <c r="R5" t="s">
-        <v>150</v>
+        <v>47</v>
       </c>
       <c r="S5" t="s">
         <v>30</v>
@@ -19331,16 +19331,16 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>182</v>
+        <v>49</v>
       </c>
       <c r="C6" t="s">
-        <v>183</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>184</v>
+        <v>51</v>
       </c>
       <c r="E6" t="s">
         <v>24</v>
@@ -19349,40 +19349,40 @@
         <v>25</v>
       </c>
       <c r="G6" t="s">
-        <v>107</v>
+        <v>26</v>
       </c>
       <c r="H6" t="s">
-        <v>149</v>
+        <v>52</v>
       </c>
       <c r="I6" t="s">
-        <v>109</v>
+        <v>28</v>
       </c>
       <c r="J6">
-        <v>1966</v>
+        <v>1994</v>
       </c>
       <c r="K6">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="L6">
-        <v>39800</v>
+        <v>1576000</v>
       </c>
       <c r="M6">
-        <v>515.75</v>
+        <v>2794</v>
       </c>
       <c r="N6">
-        <v>0.51575000000000004</v>
+        <v>2.794</v>
       </c>
       <c r="O6">
-        <v>33.93</v>
+        <v>742.77</v>
       </c>
       <c r="P6">
-        <v>57.04</v>
+        <v>13.570000000000002</v>
       </c>
       <c r="Q6" s="10">
         <v>46265</v>
       </c>
       <c r="R6" t="s">
-        <v>185</v>
+        <v>53</v>
       </c>
       <c r="S6" t="s">
         <v>30</v>
@@ -19455,16 +19455,16 @@
     </row>
     <row r="8" spans="1:20">
       <c r="A8">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="E8" t="s">
         <v>24</v>
@@ -19476,37 +19476,37 @@
         <v>26</v>
       </c>
       <c r="H8" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="I8" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="J8">
-        <v>1975</v>
+        <v>2002</v>
       </c>
       <c r="K8">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="L8">
-        <v>223000</v>
+        <v>0</v>
       </c>
       <c r="M8">
-        <v>3783</v>
+        <v>1876</v>
       </c>
       <c r="N8">
-        <v>3.7829999999999999</v>
+        <v>1.8759999999999999</v>
       </c>
       <c r="O8">
-        <v>318.27</v>
+        <v>8.76</v>
       </c>
       <c r="P8">
-        <v>48.54</v>
+        <v>-22.59</v>
       </c>
       <c r="Q8" s="10">
         <v>46265</v>
       </c>
       <c r="R8" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="S8" t="s">
         <v>30</v>
@@ -19517,16 +19517,16 @@
     </row>
     <row r="9" spans="1:20">
       <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
         <v>70</v>
       </c>
-      <c r="B9" t="s">
-        <v>434</v>
-      </c>
       <c r="C9" t="s">
-        <v>435</v>
+        <v>71</v>
       </c>
       <c r="D9" t="s">
-        <v>436</v>
+        <v>72</v>
       </c>
       <c r="E9" t="s">
         <v>24</v>
@@ -19538,37 +19538,37 @@
         <v>26</v>
       </c>
       <c r="H9" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="I9" t="s">
-        <v>109</v>
+        <v>28</v>
       </c>
       <c r="J9">
-        <v>2004</v>
+        <v>1961</v>
       </c>
       <c r="K9">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="L9">
-        <v>5115</v>
+        <v>33000</v>
       </c>
       <c r="M9">
-        <v>247.84</v>
+        <v>1757</v>
       </c>
       <c r="N9">
-        <v>0.24784</v>
+        <v>1.7569999999999999</v>
       </c>
       <c r="O9">
-        <v>9.6999999999999993</v>
+        <v>75.459999999999994</v>
       </c>
       <c r="P9">
-        <v>47.02</v>
+        <v>44.55</v>
       </c>
       <c r="Q9" s="10">
         <v>46265</v>
       </c>
       <c r="R9" t="s">
-        <v>437</v>
+        <v>73</v>
       </c>
       <c r="S9" t="s">
         <v>30</v>
@@ -19579,58 +19579,58 @@
     </row>
     <row r="10" spans="1:20">
       <c r="A10">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>217</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>218</v>
+        <v>76</v>
       </c>
       <c r="D10" t="s">
-        <v>219</v>
+        <v>77</v>
       </c>
       <c r="E10" t="s">
-        <v>172</v>
+        <v>78</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="G10" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="H10" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="I10" t="s">
-        <v>220</v>
+        <v>82</v>
       </c>
       <c r="J10">
-        <v>1954</v>
+        <v>1933</v>
       </c>
       <c r="K10">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="L10">
-        <v>378344</v>
+        <v>76664</v>
       </c>
       <c r="M10">
-        <v>427.48</v>
+        <v>1679</v>
       </c>
       <c r="N10">
-        <v>0.42748000000000003</v>
+        <v>1.679</v>
       </c>
       <c r="O10">
-        <v>112.1</v>
+        <v>459.04</v>
       </c>
       <c r="P10">
-        <v>47</v>
+        <v>42.47</v>
       </c>
       <c r="Q10" s="10">
         <v>46265</v>
       </c>
       <c r="R10" t="s">
-        <v>221</v>
+        <v>83</v>
       </c>
       <c r="S10" t="s">
         <v>30</v>
@@ -19641,16 +19641,16 @@
     </row>
     <row r="11" spans="1:20">
       <c r="A11">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>85</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="D11" t="s">
-        <v>41</v>
+        <v>87</v>
       </c>
       <c r="E11" t="s">
         <v>24</v>
@@ -19662,37 +19662,37 @@
         <v>26</v>
       </c>
       <c r="H11" t="s">
-        <v>36</v>
+        <v>88</v>
       </c>
       <c r="I11" t="s">
         <v>28</v>
       </c>
       <c r="J11">
-        <v>1998</v>
+        <v>2004</v>
       </c>
       <c r="K11">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="L11">
-        <v>190820</v>
+        <v>78865</v>
       </c>
       <c r="M11">
-        <v>4096</v>
+        <v>1457</v>
       </c>
       <c r="N11">
-        <v>4.0960000000000001</v>
+        <v>1.4570000000000001</v>
       </c>
       <c r="O11">
-        <v>422.49</v>
+        <v>214.96</v>
       </c>
       <c r="P11">
-        <v>46.31</v>
+        <v>42.23</v>
       </c>
       <c r="Q11" s="10">
         <v>46265</v>
       </c>
       <c r="R11" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="S11" t="s">
         <v>30</v>
@@ -19703,58 +19703,58 @@
     </row>
     <row r="12" spans="1:20">
       <c r="A12">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>322</v>
+        <v>91</v>
       </c>
       <c r="C12" t="s">
-        <v>323</v>
+        <v>92</v>
       </c>
       <c r="D12" t="s">
-        <v>324</v>
+        <v>93</v>
       </c>
       <c r="E12" t="s">
-        <v>172</v>
+        <v>24</v>
       </c>
       <c r="F12" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="G12" t="s">
-        <v>107</v>
+        <v>26</v>
       </c>
       <c r="H12" t="s">
-        <v>126</v>
+        <v>94</v>
       </c>
       <c r="I12" t="s">
-        <v>220</v>
+        <v>28</v>
       </c>
       <c r="J12">
-        <v>1912</v>
+        <v>2003</v>
       </c>
       <c r="K12">
-        <v>114</v>
+        <v>23</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>134785</v>
       </c>
       <c r="M12">
-        <v>312.18</v>
+        <v>1448</v>
       </c>
       <c r="N12">
-        <v>0.31218000000000001</v>
+        <v>1.448</v>
       </c>
       <c r="O12">
-        <v>95.37</v>
+        <v>97.87</v>
       </c>
       <c r="P12">
-        <v>45.09</v>
+        <v>5.9</v>
       </c>
       <c r="Q12" s="10">
         <v>46265</v>
       </c>
       <c r="R12" t="s">
-        <v>325</v>
+        <v>95</v>
       </c>
       <c r="S12" t="s">
         <v>30</v>
@@ -19765,22 +19765,22 @@
     </row>
     <row r="13" spans="1:20">
       <c r="A13">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="C13" t="s">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="E13" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="F13" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="G13" t="s">
         <v>26</v>
@@ -19789,34 +19789,34 @@
         <v>27</v>
       </c>
       <c r="I13" t="s">
-        <v>28</v>
+        <v>101</v>
       </c>
       <c r="J13">
-        <v>1961</v>
+        <v>1969</v>
       </c>
       <c r="K13">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="L13">
-        <v>33000</v>
+        <v>259149</v>
       </c>
       <c r="M13">
-        <v>1757</v>
+        <v>1248</v>
       </c>
       <c r="N13">
-        <v>1.7569999999999999</v>
+        <v>1.248</v>
       </c>
       <c r="O13">
-        <v>75.459999999999994</v>
+        <v>270.94</v>
       </c>
       <c r="P13">
-        <v>44.55</v>
+        <v>25.53</v>
       </c>
       <c r="Q13" s="10">
         <v>46265</v>
       </c>
       <c r="R13" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="S13" t="s">
         <v>30</v>
@@ -19827,16 +19827,16 @@
     </row>
     <row r="14" spans="1:20">
       <c r="A14">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>197</v>
+        <v>104</v>
       </c>
       <c r="C14" t="s">
-        <v>198</v>
+        <v>105</v>
       </c>
       <c r="D14" t="s">
-        <v>199</v>
+        <v>106</v>
       </c>
       <c r="E14" t="s">
         <v>24</v>
@@ -19845,40 +19845,40 @@
         <v>25</v>
       </c>
       <c r="G14" t="s">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="H14" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="I14" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="J14">
-        <v>2003</v>
+        <v>1839</v>
       </c>
       <c r="K14">
-        <v>23</v>
+        <v>187</v>
       </c>
       <c r="L14">
-        <v>4429</v>
+        <v>387800</v>
       </c>
       <c r="M14">
-        <v>449.94</v>
+        <v>1078</v>
       </c>
       <c r="N14">
-        <v>0.44994000000000001</v>
+        <v>1.0780000000000001</v>
       </c>
       <c r="O14">
-        <v>5.22</v>
+        <v>385.68</v>
       </c>
       <c r="P14">
-        <v>44.45</v>
+        <v>16.010000000000002</v>
       </c>
       <c r="Q14" s="10">
         <v>46265</v>
       </c>
       <c r="R14" t="s">
-        <v>200</v>
+        <v>110</v>
       </c>
       <c r="S14" t="s">
         <v>30</v>
@@ -19889,58 +19889,58 @@
     </row>
     <row r="15" spans="1:20">
       <c r="A15">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>402</v>
+        <v>112</v>
       </c>
       <c r="C15" t="s">
-        <v>403</v>
+        <v>113</v>
       </c>
       <c r="D15" t="s">
-        <v>404</v>
+        <v>114</v>
       </c>
       <c r="E15" t="s">
-        <v>405</v>
+        <v>24</v>
       </c>
       <c r="F15" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="G15" t="s">
-        <v>107</v>
+        <v>26</v>
       </c>
       <c r="H15" t="s">
-        <v>126</v>
+        <v>27</v>
       </c>
       <c r="I15" t="s">
-        <v>406</v>
+        <v>28</v>
       </c>
       <c r="J15">
-        <v>2005</v>
+        <v>1978</v>
       </c>
       <c r="K15">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="L15">
-        <v>156000</v>
+        <v>53000</v>
       </c>
       <c r="M15">
-        <v>255.87</v>
+        <v>1066</v>
       </c>
       <c r="N15">
-        <v>0.25586999999999999</v>
+        <v>1.0660000000000001</v>
       </c>
       <c r="O15">
-        <v>49.47</v>
+        <v>90.27</v>
       </c>
       <c r="P15">
-        <v>44.37</v>
+        <v>25.82</v>
       </c>
       <c r="Q15" s="10">
         <v>46265</v>
       </c>
       <c r="R15" t="s">
-        <v>407</v>
+        <v>115</v>
       </c>
       <c r="S15" t="s">
         <v>30</v>
@@ -19951,58 +19951,58 @@
     </row>
     <row r="16" spans="1:20">
       <c r="A16">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>262</v>
+        <v>117</v>
       </c>
       <c r="C16" t="s">
-        <v>263</v>
+        <v>118</v>
       </c>
       <c r="D16" t="s">
-        <v>264</v>
+        <v>119</v>
       </c>
       <c r="E16" t="s">
-        <v>172</v>
+        <v>24</v>
       </c>
       <c r="F16" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="G16" t="s">
-        <v>107</v>
+        <v>26</v>
       </c>
       <c r="H16" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="I16" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="J16">
-        <v>1951</v>
+        <v>1876</v>
       </c>
       <c r="K16">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="L16">
-        <v>457835</v>
+        <v>33000</v>
       </c>
       <c r="M16">
-        <v>361.05</v>
+        <v>1034</v>
       </c>
       <c r="N16">
-        <v>0.36105000000000004</v>
+        <v>1.034</v>
       </c>
       <c r="O16">
-        <v>105.69</v>
+        <v>72.239999999999995</v>
       </c>
       <c r="P16">
-        <v>43.65</v>
+        <v>43.07</v>
       </c>
       <c r="Q16" s="10">
         <v>46265</v>
       </c>
       <c r="R16" t="s">
-        <v>265</v>
+        <v>121</v>
       </c>
       <c r="S16" t="s">
         <v>30</v>
@@ -20013,58 +20013,58 @@
     </row>
     <row r="17" spans="1:20">
       <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>123</v>
+      </c>
+      <c r="C17" t="s">
+        <v>124</v>
+      </c>
+      <c r="D17" t="s">
+        <v>125</v>
+      </c>
+      <c r="E17" t="s">
         <v>24</v>
       </c>
-      <c r="B17" t="s">
-        <v>169</v>
-      </c>
-      <c r="C17" t="s">
-        <v>170</v>
-      </c>
-      <c r="D17" t="s">
-        <v>171</v>
-      </c>
-      <c r="E17" t="s">
-        <v>172</v>
-      </c>
       <c r="F17" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="G17" t="s">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="H17" t="s">
-        <v>27</v>
+        <v>126</v>
       </c>
       <c r="I17" t="s">
-        <v>173</v>
+        <v>109</v>
       </c>
       <c r="J17">
-        <v>2016</v>
+        <v>1799</v>
       </c>
       <c r="K17">
-        <v>10</v>
+        <v>227</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>318512</v>
       </c>
       <c r="M17">
-        <v>611.37</v>
+        <v>944.99</v>
       </c>
       <c r="N17">
-        <v>0.61136999999999997</v>
+        <v>0.94499</v>
       </c>
       <c r="O17">
-        <v>15.24</v>
+        <v>186.94</v>
       </c>
       <c r="P17">
-        <v>43.19</v>
+        <v>39.94</v>
       </c>
       <c r="Q17" s="10">
         <v>46265</v>
       </c>
       <c r="R17" t="s">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="S17" t="s">
         <v>30</v>
@@ -20075,58 +20075,58 @@
     </row>
     <row r="18" spans="1:20">
       <c r="A18">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="C18" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="D18" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="E18" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="F18" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="G18" t="s">
         <v>26</v>
       </c>
       <c r="H18" t="s">
-        <v>120</v>
+        <v>27</v>
       </c>
       <c r="I18" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="J18">
-        <v>1876</v>
+        <v>1983</v>
       </c>
       <c r="K18">
-        <v>150</v>
+        <v>43</v>
       </c>
       <c r="L18">
-        <v>33000</v>
+        <v>0</v>
       </c>
       <c r="M18">
-        <v>1034</v>
+        <v>868.67</v>
       </c>
       <c r="N18">
-        <v>1.034</v>
+        <v>0.86866999999999994</v>
       </c>
       <c r="O18">
-        <v>72.239999999999995</v>
+        <v>91.71</v>
       </c>
       <c r="P18">
-        <v>43.07</v>
+        <v>70.87</v>
       </c>
       <c r="Q18" s="10">
         <v>46265</v>
       </c>
       <c r="R18" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="S18" t="s">
         <v>30</v>
@@ -20137,58 +20137,58 @@
     </row>
     <row r="19" spans="1:20">
       <c r="A19">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>135</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c r="D19" t="s">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="E19" t="s">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="F19" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="G19" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="H19" t="s">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="I19" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="J19">
-        <v>1933</v>
+        <v>1962</v>
       </c>
       <c r="K19">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="L19">
-        <v>76664</v>
+        <v>2100000</v>
       </c>
       <c r="M19">
-        <v>1679</v>
+        <v>835.12</v>
       </c>
       <c r="N19">
-        <v>1.679</v>
+        <v>0.83511999999999997</v>
       </c>
       <c r="O19">
-        <v>459.04</v>
+        <v>725.3</v>
       </c>
       <c r="P19">
-        <v>42.47</v>
+        <v>4.13</v>
       </c>
       <c r="Q19" s="10">
         <v>46265</v>
       </c>
       <c r="R19" t="s">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="S19" t="s">
         <v>30</v>
@@ -20199,16 +20199,16 @@
     </row>
     <row r="20" spans="1:20">
       <c r="A20">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>142</v>
       </c>
       <c r="C20" t="s">
-        <v>86</v>
+        <v>143</v>
       </c>
       <c r="D20" t="s">
-        <v>87</v>
+        <v>143</v>
       </c>
       <c r="E20" t="s">
         <v>24</v>
@@ -20220,37 +20220,37 @@
         <v>26</v>
       </c>
       <c r="H20" t="s">
-        <v>88</v>
+        <v>27</v>
       </c>
       <c r="I20" t="s">
         <v>28</v>
       </c>
       <c r="J20">
-        <v>2004</v>
+        <v>1969</v>
       </c>
       <c r="K20">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="L20">
-        <v>78865</v>
+        <v>31000</v>
       </c>
       <c r="M20">
-        <v>1457</v>
+        <v>764.34</v>
       </c>
       <c r="N20">
-        <v>1.4570000000000001</v>
+        <v>0.76434000000000002</v>
       </c>
       <c r="O20">
-        <v>214.96</v>
+        <v>37.450000000000003</v>
       </c>
       <c r="P20">
-        <v>42.23</v>
+        <v>11.95</v>
       </c>
       <c r="Q20" s="10">
         <v>46265</v>
       </c>
       <c r="R20" t="s">
-        <v>89</v>
+        <v>144</v>
       </c>
       <c r="S20" t="s">
         <v>30</v>
@@ -20261,58 +20261,58 @@
     </row>
     <row r="21" spans="1:20">
       <c r="A21">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>565</v>
+        <v>146</v>
       </c>
       <c r="C21" t="s">
-        <v>566</v>
+        <v>147</v>
       </c>
       <c r="D21" t="s">
-        <v>567</v>
+        <v>148</v>
       </c>
       <c r="E21" t="s">
-        <v>568</v>
+        <v>24</v>
       </c>
       <c r="F21" t="s">
-        <v>160</v>
+        <v>25</v>
       </c>
       <c r="G21" t="s">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="H21" t="s">
-        <v>120</v>
+        <v>149</v>
       </c>
       <c r="I21" t="s">
-        <v>569</v>
+        <v>109</v>
       </c>
       <c r="J21">
-        <v>1923</v>
+        <v>1958</v>
       </c>
       <c r="K21">
-        <v>103</v>
+        <v>68</v>
       </c>
       <c r="L21">
-        <v>69505</v>
+        <v>34100</v>
       </c>
       <c r="M21">
-        <v>200.31</v>
+        <v>709.08</v>
       </c>
       <c r="N21">
-        <v>0.20031000000000002</v>
+        <v>0.70908000000000004</v>
       </c>
       <c r="O21">
-        <v>51.37</v>
+        <v>43.02</v>
       </c>
       <c r="P21">
-        <v>42.23</v>
+        <v>61.480000000000004</v>
       </c>
       <c r="Q21" s="10">
         <v>46265</v>
       </c>
       <c r="R21" t="s">
-        <v>570</v>
+        <v>150</v>
       </c>
       <c r="S21" t="s">
         <v>30</v>
@@ -20323,58 +20323,58 @@
     </row>
     <row r="22" spans="1:20">
       <c r="A22">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>274</v>
+        <v>152</v>
       </c>
       <c r="C22" t="s">
-        <v>275</v>
+        <v>153</v>
       </c>
       <c r="D22" t="s">
-        <v>275</v>
+        <v>154</v>
       </c>
       <c r="E22" t="s">
-        <v>276</v>
+        <v>24</v>
       </c>
       <c r="F22" t="s">
-        <v>160</v>
+        <v>25</v>
       </c>
       <c r="G22" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="H22" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="I22" t="s">
-        <v>277</v>
+        <v>109</v>
       </c>
       <c r="J22">
-        <v>1865</v>
+        <v>1870</v>
       </c>
       <c r="K22">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="L22">
-        <v>211479</v>
+        <v>58000</v>
       </c>
       <c r="M22">
-        <v>352.76</v>
+        <v>659.26</v>
       </c>
       <c r="N22">
-        <v>0.35276000000000002</v>
+        <v>0.65925999999999996</v>
       </c>
       <c r="O22">
-        <v>72.400000000000006</v>
+        <v>326</v>
       </c>
       <c r="P22">
-        <v>41.15</v>
+        <v>11.23</v>
       </c>
       <c r="Q22" s="10">
         <v>46265</v>
       </c>
       <c r="R22" t="s">
-        <v>278</v>
+        <v>155</v>
       </c>
       <c r="S22" t="s">
         <v>30</v>
@@ -20385,22 +20385,22 @@
     </row>
     <row r="23" spans="1:20">
       <c r="A23">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>496</v>
+        <v>157</v>
       </c>
       <c r="C23" t="s">
-        <v>497</v>
+        <v>158</v>
       </c>
       <c r="D23" t="s">
-        <v>498</v>
+        <v>158</v>
       </c>
       <c r="E23" t="s">
-        <v>24</v>
+        <v>159</v>
       </c>
       <c r="F23" t="s">
-        <v>25</v>
+        <v>160</v>
       </c>
       <c r="G23" t="s">
         <v>26</v>
@@ -20409,34 +20409,34 @@
         <v>27</v>
       </c>
       <c r="I23" t="s">
-        <v>28</v>
+        <v>161</v>
       </c>
       <c r="J23">
-        <v>1975</v>
+        <v>1984</v>
       </c>
       <c r="K23">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="L23">
-        <v>17200</v>
+        <v>44175</v>
       </c>
       <c r="M23">
-        <v>229.12</v>
+        <v>649.33000000000004</v>
       </c>
       <c r="N23">
-        <v>0.22912000000000002</v>
+        <v>0.64933000000000007</v>
       </c>
       <c r="O23">
-        <v>13.09</v>
+        <v>41.02</v>
       </c>
       <c r="P23">
-        <v>41.11</v>
+        <v>34.909999999999997</v>
       </c>
       <c r="Q23" s="10">
         <v>46265</v>
       </c>
       <c r="R23" t="s">
-        <v>499</v>
+        <v>162</v>
       </c>
       <c r="S23" t="s">
         <v>30</v>
@@ -20447,58 +20447,58 @@
     </row>
     <row r="24" spans="1:20">
       <c r="A24">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>360</v>
+        <v>164</v>
       </c>
       <c r="C24" t="s">
-        <v>361</v>
+        <v>165</v>
       </c>
       <c r="D24" t="s">
-        <v>362</v>
+        <v>166</v>
       </c>
       <c r="E24" t="s">
-        <v>363</v>
+        <v>24</v>
       </c>
       <c r="F24" t="s">
         <v>25</v>
       </c>
       <c r="G24" t="s">
-        <v>107</v>
+        <v>26</v>
       </c>
       <c r="H24" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="I24" t="s">
-        <v>364</v>
+        <v>109</v>
       </c>
       <c r="J24">
-        <v>1864</v>
+        <v>1886</v>
       </c>
       <c r="K24">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="L24">
-        <v>91427</v>
+        <v>138200</v>
       </c>
       <c r="M24">
-        <v>282.16000000000003</v>
+        <v>641.34</v>
       </c>
       <c r="N24">
-        <v>0.28216000000000002</v>
+        <v>0.64134000000000002</v>
       </c>
       <c r="O24">
-        <v>50.53</v>
+        <v>96.36</v>
       </c>
       <c r="P24">
-        <v>40.590000000000003</v>
+        <v>34.58</v>
       </c>
       <c r="Q24" s="10">
         <v>46265</v>
       </c>
       <c r="R24" t="s">
-        <v>365</v>
+        <v>167</v>
       </c>
       <c r="S24" t="s">
         <v>30</v>
@@ -20509,58 +20509,58 @@
     </row>
     <row r="25" spans="1:20">
       <c r="A25">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>123</v>
+        <v>169</v>
       </c>
       <c r="C25" t="s">
-        <v>124</v>
+        <v>170</v>
       </c>
       <c r="D25" t="s">
-        <v>125</v>
+        <v>171</v>
       </c>
       <c r="E25" t="s">
-        <v>24</v>
+        <v>172</v>
       </c>
       <c r="F25" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="G25" t="s">
-        <v>107</v>
+        <v>26</v>
       </c>
       <c r="H25" t="s">
-        <v>126</v>
+        <v>27</v>
       </c>
       <c r="I25" t="s">
-        <v>109</v>
+        <v>173</v>
       </c>
       <c r="J25">
-        <v>1799</v>
+        <v>2016</v>
       </c>
       <c r="K25">
-        <v>227</v>
+        <v>10</v>
       </c>
       <c r="L25">
-        <v>318512</v>
+        <v>0</v>
       </c>
       <c r="M25">
-        <v>944.99</v>
+        <v>611.37</v>
       </c>
       <c r="N25">
-        <v>0.94499</v>
+        <v>0.61136999999999997</v>
       </c>
       <c r="O25">
-        <v>186.94</v>
+        <v>15.24</v>
       </c>
       <c r="P25">
-        <v>39.94</v>
+        <v>43.19</v>
       </c>
       <c r="Q25" s="10">
         <v>46265</v>
       </c>
       <c r="R25" t="s">
-        <v>127</v>
+        <v>174</v>
       </c>
       <c r="S25" t="s">
         <v>30</v>
@@ -20571,58 +20571,58 @@
     </row>
     <row r="26" spans="1:20">
       <c r="A26">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>445</v>
+        <v>176</v>
       </c>
       <c r="C26" t="s">
-        <v>446</v>
+        <v>177</v>
       </c>
       <c r="D26" t="s">
-        <v>447</v>
+        <v>178</v>
       </c>
       <c r="E26" t="s">
-        <v>448</v>
+        <v>172</v>
       </c>
       <c r="F26" t="s">
         <v>59</v>
       </c>
       <c r="G26" t="s">
-        <v>449</v>
+        <v>26</v>
       </c>
       <c r="H26" t="s">
-        <v>450</v>
+        <v>88</v>
       </c>
       <c r="I26" t="s">
-        <v>451</v>
+        <v>179</v>
       </c>
       <c r="J26">
-        <v>1885</v>
+        <v>1998</v>
       </c>
       <c r="K26">
-        <v>141</v>
+        <v>28</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>87412</v>
       </c>
       <c r="M26">
-        <v>238.54</v>
+        <v>516.34</v>
       </c>
       <c r="N26">
-        <v>0.23854</v>
+        <v>0.51634000000000002</v>
       </c>
       <c r="O26">
-        <v>58.76</v>
+        <v>111.76</v>
       </c>
       <c r="P26">
-        <v>39.450000000000003</v>
+        <v>36.869999999999997</v>
       </c>
       <c r="Q26" s="10">
         <v>46265</v>
       </c>
       <c r="R26" t="s">
-        <v>453</v>
+        <v>180</v>
       </c>
       <c r="S26" t="s">
         <v>30</v>
@@ -20633,16 +20633,16 @@
     </row>
     <row r="27" spans="1:20">
       <c r="A27">
-        <v>88</v>
+        <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>537</v>
+        <v>182</v>
       </c>
       <c r="C27" t="s">
-        <v>538</v>
+        <v>183</v>
       </c>
       <c r="D27" t="s">
-        <v>539</v>
+        <v>184</v>
       </c>
       <c r="E27" t="s">
         <v>24</v>
@@ -20651,40 +20651,40 @@
         <v>25</v>
       </c>
       <c r="G27" t="s">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="H27" t="s">
-        <v>66</v>
+        <v>149</v>
       </c>
       <c r="I27" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="J27">
-        <v>1988</v>
+        <v>1966</v>
       </c>
       <c r="K27">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="L27">
-        <v>11100</v>
+        <v>39800</v>
       </c>
       <c r="M27">
-        <v>215.08</v>
+        <v>515.75</v>
       </c>
       <c r="N27">
-        <v>0.21508000000000002</v>
+        <v>0.51575000000000004</v>
       </c>
       <c r="O27">
-        <v>13.18</v>
+        <v>33.93</v>
       </c>
       <c r="P27">
-        <v>39.06</v>
+        <v>57.04</v>
       </c>
       <c r="Q27" s="10">
         <v>46265</v>
       </c>
       <c r="R27" t="s">
-        <v>540</v>
+        <v>185</v>
       </c>
       <c r="S27" t="s">
         <v>30</v>
@@ -20695,16 +20695,16 @@
     </row>
     <row r="28" spans="1:20">
       <c r="A28">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>337</v>
+        <v>187</v>
       </c>
       <c r="C28" t="s">
-        <v>338</v>
+        <v>188</v>
       </c>
       <c r="D28" t="s">
-        <v>339</v>
+        <v>189</v>
       </c>
       <c r="E28" t="s">
         <v>24</v>
@@ -20713,40 +20713,40 @@
         <v>25</v>
       </c>
       <c r="G28" t="s">
-        <v>107</v>
+        <v>26</v>
       </c>
       <c r="H28" t="s">
-        <v>126</v>
+        <v>27</v>
       </c>
       <c r="I28" t="s">
-        <v>109</v>
+        <v>28</v>
       </c>
       <c r="J28">
-        <v>1869</v>
+        <v>1968</v>
       </c>
       <c r="K28">
-        <v>157</v>
+        <v>58</v>
       </c>
       <c r="L28">
-        <v>47400</v>
+        <v>85100</v>
       </c>
       <c r="M28">
-        <v>298.99</v>
+        <v>472.57</v>
       </c>
       <c r="N28">
-        <v>0.29899000000000003</v>
+        <v>0.47256999999999999</v>
       </c>
       <c r="O28">
-        <v>60.44</v>
+        <v>53.76</v>
       </c>
       <c r="P28">
-        <v>37.53</v>
+        <v>2.94</v>
       </c>
       <c r="Q28" s="10">
         <v>46265</v>
       </c>
       <c r="R28" t="s">
-        <v>340</v>
+        <v>190</v>
       </c>
       <c r="S28" t="s">
         <v>30</v>
@@ -20757,58 +20757,58 @@
     </row>
     <row r="29" spans="1:20">
       <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>192</v>
+      </c>
+      <c r="C29" t="s">
+        <v>193</v>
+      </c>
+      <c r="D29" t="s">
+        <v>194</v>
+      </c>
+      <c r="E29" t="s">
+        <v>24</v>
+      </c>
+      <c r="F29" t="s">
         <v>25</v>
-      </c>
-      <c r="B29" t="s">
-        <v>176</v>
-      </c>
-      <c r="C29" t="s">
-        <v>177</v>
-      </c>
-      <c r="D29" t="s">
-        <v>178</v>
-      </c>
-      <c r="E29" t="s">
-        <v>172</v>
-      </c>
-      <c r="F29" t="s">
-        <v>59</v>
       </c>
       <c r="G29" t="s">
         <v>26</v>
       </c>
       <c r="H29" t="s">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="I29" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="J29">
-        <v>1998</v>
+        <v>2013</v>
       </c>
       <c r="K29">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="L29">
-        <v>87412</v>
+        <v>57000</v>
       </c>
       <c r="M29">
-        <v>516.34</v>
+        <v>455.42</v>
       </c>
       <c r="N29">
-        <v>0.51634000000000002</v>
+        <v>0.45541999999999999</v>
       </c>
       <c r="O29">
-        <v>111.76</v>
+        <v>62.81</v>
       </c>
       <c r="P29">
-        <v>36.869999999999997</v>
+        <v>9.51</v>
       </c>
       <c r="Q29" s="10">
         <v>46265</v>
       </c>
       <c r="R29" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="S29" t="s">
         <v>30</v>
@@ -20819,58 +20819,58 @@
     </row>
     <row r="30" spans="1:20">
       <c r="A30">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>157</v>
+        <v>197</v>
       </c>
       <c r="C30" t="s">
-        <v>158</v>
+        <v>198</v>
       </c>
       <c r="D30" t="s">
-        <v>158</v>
+        <v>199</v>
       </c>
       <c r="E30" t="s">
-        <v>159</v>
+        <v>24</v>
       </c>
       <c r="F30" t="s">
-        <v>160</v>
+        <v>25</v>
       </c>
       <c r="G30" t="s">
         <v>26</v>
       </c>
       <c r="H30" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="I30" t="s">
-        <v>161</v>
+        <v>28</v>
       </c>
       <c r="J30">
-        <v>1984</v>
+        <v>2003</v>
       </c>
       <c r="K30">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="L30">
-        <v>44175</v>
+        <v>4429</v>
       </c>
       <c r="M30">
-        <v>649.33000000000004</v>
+        <v>449.94</v>
       </c>
       <c r="N30">
-        <v>0.64933000000000007</v>
+        <v>0.44994000000000001</v>
       </c>
       <c r="O30">
-        <v>41.02</v>
+        <v>5.22</v>
       </c>
       <c r="P30">
-        <v>34.909999999999997</v>
+        <v>44.45</v>
       </c>
       <c r="Q30" s="10">
         <v>46265</v>
       </c>
       <c r="R30" t="s">
-        <v>162</v>
+        <v>200</v>
       </c>
       <c r="S30" t="s">
         <v>30</v>
@@ -20881,16 +20881,16 @@
     </row>
     <row r="31" spans="1:20">
       <c r="A31">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>164</v>
+        <v>202</v>
       </c>
       <c r="C31" t="s">
-        <v>165</v>
+        <v>203</v>
       </c>
       <c r="D31" t="s">
-        <v>166</v>
+        <v>204</v>
       </c>
       <c r="E31" t="s">
         <v>24</v>
@@ -20902,37 +20902,37 @@
         <v>26</v>
       </c>
       <c r="H31" t="s">
-        <v>120</v>
+        <v>66</v>
       </c>
       <c r="I31" t="s">
-        <v>109</v>
+        <v>28</v>
       </c>
       <c r="J31">
-        <v>1886</v>
+        <v>1984</v>
       </c>
       <c r="K31">
-        <v>140</v>
+        <v>42</v>
       </c>
       <c r="L31">
-        <v>138200</v>
+        <v>86200</v>
       </c>
       <c r="M31">
-        <v>641.34</v>
+        <v>436.49</v>
       </c>
       <c r="N31">
-        <v>0.64134000000000002</v>
+        <v>0.43648999999999999</v>
       </c>
       <c r="O31">
-        <v>96.36</v>
+        <v>60.74</v>
       </c>
       <c r="P31">
-        <v>34.58</v>
+        <v>19.59</v>
       </c>
       <c r="Q31" s="10">
         <v>46265</v>
       </c>
       <c r="R31" t="s">
-        <v>167</v>
+        <v>205</v>
       </c>
       <c r="S31" t="s">
         <v>30</v>
@@ -20943,16 +20943,16 @@
     </row>
     <row r="32" spans="1:20">
       <c r="A32">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>240</v>
+        <v>207</v>
       </c>
       <c r="C32" t="s">
-        <v>241</v>
+        <v>208</v>
       </c>
       <c r="D32" t="s">
-        <v>242</v>
+        <v>209</v>
       </c>
       <c r="E32" t="s">
         <v>24</v>
@@ -20961,40 +20961,40 @@
         <v>25</v>
       </c>
       <c r="G32" t="s">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="H32" t="s">
-        <v>27</v>
+        <v>126</v>
       </c>
       <c r="I32" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="J32">
-        <v>1980</v>
+        <v>1784</v>
       </c>
       <c r="K32">
-        <v>46</v>
+        <v>242</v>
       </c>
       <c r="L32">
-        <v>23300</v>
+        <v>213000</v>
       </c>
       <c r="M32">
-        <v>376.17</v>
+        <v>432.95</v>
       </c>
       <c r="N32">
-        <v>0.37617</v>
+        <v>0.43295</v>
       </c>
       <c r="O32">
-        <v>21.68</v>
+        <v>116</v>
       </c>
       <c r="P32">
-        <v>34.520000000000003</v>
+        <v>34.46</v>
       </c>
       <c r="Q32" s="10">
         <v>46265</v>
       </c>
       <c r="R32" t="s">
-        <v>243</v>
+        <v>210</v>
       </c>
       <c r="S32" t="s">
         <v>30</v>
@@ -21005,16 +21005,16 @@
     </row>
     <row r="33" spans="1:20">
       <c r="A33">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C33" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="D33" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E33" t="s">
         <v>24</v>
@@ -21023,40 +21023,40 @@
         <v>25</v>
       </c>
       <c r="G33" t="s">
-        <v>107</v>
+        <v>26</v>
       </c>
       <c r="H33" t="s">
-        <v>126</v>
+        <v>36</v>
       </c>
       <c r="I33" t="s">
         <v>109</v>
       </c>
       <c r="J33">
-        <v>1784</v>
+        <v>1977</v>
       </c>
       <c r="K33">
-        <v>242</v>
+        <v>49</v>
       </c>
       <c r="L33">
-        <v>213000</v>
+        <v>141000</v>
       </c>
       <c r="M33">
-        <v>432.95</v>
+        <v>431.29</v>
       </c>
       <c r="N33">
-        <v>0.43295</v>
+        <v>0.43129000000000001</v>
       </c>
       <c r="O33">
-        <v>116</v>
+        <v>67.349999999999994</v>
       </c>
       <c r="P33">
-        <v>34.46</v>
+        <v>29.03</v>
       </c>
       <c r="Q33" s="10">
         <v>46265</v>
       </c>
       <c r="R33" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="S33" t="s">
         <v>30</v>
@@ -21067,58 +21067,58 @@
     </row>
     <row r="34" spans="1:20">
       <c r="A34">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>342</v>
+        <v>217</v>
       </c>
       <c r="C34" t="s">
-        <v>343</v>
+        <v>218</v>
       </c>
       <c r="D34" t="s">
-        <v>344</v>
+        <v>219</v>
       </c>
       <c r="E34" t="s">
-        <v>24</v>
+        <v>172</v>
       </c>
       <c r="F34" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="G34" t="s">
-        <v>236</v>
+        <v>107</v>
       </c>
       <c r="H34" t="s">
-        <v>345</v>
+        <v>126</v>
       </c>
       <c r="I34" t="s">
-        <v>109</v>
+        <v>220</v>
       </c>
       <c r="J34">
-        <v>2008</v>
+        <v>1954</v>
       </c>
       <c r="K34">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="L34">
-        <v>84900</v>
+        <v>378344</v>
       </c>
       <c r="M34">
-        <v>293.05</v>
+        <v>427.48</v>
       </c>
       <c r="N34">
-        <v>0.29305000000000003</v>
+        <v>0.42748000000000003</v>
       </c>
       <c r="O34">
-        <v>41.49</v>
+        <v>112.1</v>
       </c>
       <c r="P34">
-        <v>34.14</v>
+        <v>47</v>
       </c>
       <c r="Q34" s="10">
         <v>46265</v>
       </c>
       <c r="R34" t="s">
-        <v>346</v>
+        <v>221</v>
       </c>
       <c r="S34" t="s">
         <v>30</v>
@@ -21129,16 +21129,16 @@
     </row>
     <row r="35" spans="1:20">
       <c r="A35">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>312</v>
+        <v>223</v>
       </c>
       <c r="C35" t="s">
-        <v>313</v>
+        <v>224</v>
       </c>
       <c r="D35" t="s">
-        <v>314</v>
+        <v>225</v>
       </c>
       <c r="E35" t="s">
         <v>24</v>
@@ -21147,40 +21147,40 @@
         <v>25</v>
       </c>
       <c r="G35" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="H35" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="I35" t="s">
-        <v>109</v>
+        <v>28</v>
       </c>
       <c r="J35">
-        <v>1935</v>
+        <v>1983</v>
       </c>
       <c r="K35">
-        <v>91</v>
+        <v>43</v>
       </c>
       <c r="L35">
-        <v>83000</v>
+        <v>341000</v>
       </c>
       <c r="M35">
-        <v>335.23</v>
+        <v>418.36</v>
       </c>
       <c r="N35">
-        <v>0.33523000000000003</v>
+        <v>0.41836000000000001</v>
       </c>
       <c r="O35">
-        <v>68.77</v>
+        <v>293.58</v>
       </c>
       <c r="P35">
-        <v>34.049999999999997</v>
+        <v>3.93</v>
       </c>
       <c r="Q35" s="10">
         <v>46265</v>
       </c>
       <c r="R35" t="s">
-        <v>315</v>
+        <v>226</v>
       </c>
       <c r="S35" t="s">
         <v>30</v>
@@ -21191,16 +21191,16 @@
     </row>
     <row r="36" spans="1:20">
       <c r="A36">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C36" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D36" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="E36" t="s">
         <v>24</v>
@@ -21209,40 +21209,40 @@
         <v>25</v>
       </c>
       <c r="G36" t="s">
-        <v>236</v>
+        <v>80</v>
       </c>
       <c r="H36" t="s">
-        <v>237</v>
+        <v>81</v>
       </c>
       <c r="I36" t="s">
         <v>109</v>
       </c>
       <c r="J36">
-        <v>1886</v>
+        <v>1879</v>
       </c>
       <c r="K36">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="L36">
-        <v>65900</v>
+        <v>43039</v>
       </c>
       <c r="M36">
-        <v>382.15</v>
+        <v>403.25</v>
       </c>
       <c r="N36">
-        <v>0.38214999999999999</v>
+        <v>0.40325</v>
       </c>
       <c r="O36">
-        <v>49.28</v>
+        <v>185.88</v>
       </c>
       <c r="P36">
-        <v>33.369999999999997</v>
+        <v>10.46</v>
       </c>
       <c r="Q36" s="10">
         <v>46265</v>
       </c>
       <c r="R36" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="S36" t="s">
         <v>30</v>
@@ -21253,16 +21253,16 @@
     </row>
     <row r="37" spans="1:20">
       <c r="A37">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>257</v>
+        <v>233</v>
       </c>
       <c r="C37" t="s">
-        <v>258</v>
+        <v>234</v>
       </c>
       <c r="D37" t="s">
-        <v>259</v>
+        <v>235</v>
       </c>
       <c r="E37" t="s">
         <v>24</v>
@@ -21271,40 +21271,40 @@
         <v>25</v>
       </c>
       <c r="G37" t="s">
-        <v>26</v>
+        <v>236</v>
       </c>
       <c r="H37" t="s">
-        <v>27</v>
+        <v>237</v>
       </c>
       <c r="I37" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="J37">
-        <v>1967</v>
+        <v>1886</v>
       </c>
       <c r="K37">
-        <v>59</v>
+        <v>140</v>
       </c>
       <c r="L37">
-        <v>36500</v>
+        <v>65900</v>
       </c>
       <c r="M37">
-        <v>362.83</v>
+        <v>382.15</v>
       </c>
       <c r="N37">
-        <v>0.36282999999999999</v>
+        <v>0.38214999999999999</v>
       </c>
       <c r="O37">
-        <v>29.02</v>
+        <v>49.28</v>
       </c>
       <c r="P37">
-        <v>32.68</v>
+        <v>33.369999999999997</v>
       </c>
       <c r="Q37" s="10">
         <v>46265</v>
       </c>
       <c r="R37" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
       <c r="S37" t="s">
         <v>30</v>
@@ -21315,16 +21315,16 @@
     </row>
     <row r="38" spans="1:20">
       <c r="A38">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="C38" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="D38" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="E38" t="s">
         <v>24</v>
@@ -21336,37 +21336,37 @@
         <v>26</v>
       </c>
       <c r="H38" t="s">
-        <v>120</v>
+        <v>27</v>
       </c>
       <c r="I38" t="s">
-        <v>109</v>
+        <v>28</v>
       </c>
       <c r="J38">
-        <v>1891</v>
+        <v>1980</v>
       </c>
       <c r="K38">
-        <v>135</v>
+        <v>46</v>
       </c>
       <c r="L38">
-        <v>75000</v>
+        <v>23300</v>
       </c>
       <c r="M38">
-        <v>365.65</v>
+        <v>376.17</v>
       </c>
       <c r="N38">
-        <v>0.36564999999999998</v>
+        <v>0.37617</v>
       </c>
       <c r="O38">
-        <v>65.760000000000005</v>
+        <v>21.68</v>
       </c>
       <c r="P38">
-        <v>32.4</v>
+        <v>34.520000000000003</v>
       </c>
       <c r="Q38" s="10">
         <v>46265</v>
       </c>
       <c r="R38" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="S38" t="s">
         <v>30</v>
@@ -21377,16 +21377,16 @@
     </row>
     <row r="39" spans="1:20">
       <c r="A39">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>455</v>
+        <v>245</v>
       </c>
       <c r="C39" t="s">
-        <v>456</v>
+        <v>246</v>
       </c>
       <c r="D39" t="s">
-        <v>457</v>
+        <v>247</v>
       </c>
       <c r="E39" t="s">
         <v>24</v>
@@ -21395,40 +21395,40 @@
         <v>25</v>
       </c>
       <c r="G39" t="s">
-        <v>26</v>
+        <v>248</v>
       </c>
       <c r="H39" t="s">
-        <v>27</v>
+        <v>249</v>
       </c>
       <c r="I39" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="J39">
-        <v>1930</v>
+        <v>1925</v>
       </c>
       <c r="K39">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="L39">
-        <v>33000</v>
+        <v>118000</v>
       </c>
       <c r="M39">
-        <v>238.28</v>
+        <v>365.84</v>
       </c>
       <c r="N39">
-        <v>0.23827999999999999</v>
+        <v>0.36584</v>
       </c>
       <c r="O39">
-        <v>18.43</v>
+        <v>70.75</v>
       </c>
       <c r="P39">
-        <v>32.29</v>
+        <v>17.07</v>
       </c>
       <c r="Q39" s="10">
         <v>46265</v>
       </c>
       <c r="R39" t="s">
-        <v>458</v>
+        <v>250</v>
       </c>
       <c r="S39" t="s">
         <v>30</v>
@@ -21439,58 +21439,58 @@
     </row>
     <row r="40" spans="1:20">
       <c r="A40">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>547</v>
+        <v>252</v>
       </c>
       <c r="C40" t="s">
-        <v>548</v>
+        <v>253</v>
       </c>
       <c r="D40" t="s">
-        <v>549</v>
+        <v>254</v>
       </c>
       <c r="E40" t="s">
-        <v>550</v>
+        <v>24</v>
       </c>
       <c r="F40" t="s">
-        <v>160</v>
+        <v>25</v>
       </c>
       <c r="G40" t="s">
-        <v>107</v>
+        <v>26</v>
       </c>
       <c r="H40" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="I40" t="s">
-        <v>551</v>
+        <v>109</v>
       </c>
       <c r="J40">
-        <v>1857</v>
+        <v>1891</v>
       </c>
       <c r="K40">
-        <v>169</v>
+        <v>135</v>
       </c>
       <c r="L40">
-        <v>198403</v>
+        <v>75000</v>
       </c>
       <c r="M40">
-        <v>211.82</v>
+        <v>365.65</v>
       </c>
       <c r="N40">
-        <v>0.21181999999999998</v>
+        <v>0.36564999999999998</v>
       </c>
       <c r="O40">
-        <v>69</v>
+        <v>65.760000000000005</v>
       </c>
       <c r="P40">
-        <v>32.270000000000003</v>
+        <v>32.4</v>
       </c>
       <c r="Q40" s="10">
         <v>46265</v>
       </c>
       <c r="R40" t="s">
-        <v>552</v>
+        <v>255</v>
       </c>
       <c r="S40" t="s">
         <v>30</v>
@@ -21501,16 +21501,16 @@
     </row>
     <row r="41" spans="1:20">
       <c r="A41">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>33</v>
+        <v>257</v>
       </c>
       <c r="C41" t="s">
-        <v>34</v>
+        <v>258</v>
       </c>
       <c r="D41" t="s">
-        <v>35</v>
+        <v>259</v>
       </c>
       <c r="E41" t="s">
         <v>24</v>
@@ -21522,37 +21522,37 @@
         <v>26</v>
       </c>
       <c r="H41" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="I41" t="s">
         <v>28</v>
       </c>
       <c r="J41">
-        <v>1976</v>
+        <v>1967</v>
       </c>
       <c r="K41">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="L41">
-        <v>166000</v>
+        <v>36500</v>
       </c>
       <c r="M41">
-        <v>4609</v>
+        <v>362.83</v>
       </c>
       <c r="N41">
-        <v>4.609</v>
+        <v>0.36282999999999999</v>
       </c>
       <c r="O41">
-        <v>451.44</v>
+        <v>29.02</v>
       </c>
       <c r="P41">
-        <v>31.89</v>
+        <v>32.68</v>
       </c>
       <c r="Q41" s="10">
         <v>46265</v>
       </c>
       <c r="R41" t="s">
-        <v>37</v>
+        <v>260</v>
       </c>
       <c r="S41" t="s">
         <v>30</v>
@@ -21563,22 +21563,22 @@
     </row>
     <row r="42" spans="1:20">
       <c r="A42">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>371</v>
+        <v>262</v>
       </c>
       <c r="C42" t="s">
-        <v>372</v>
+        <v>263</v>
       </c>
       <c r="D42" t="s">
-        <v>373</v>
+        <v>264</v>
       </c>
       <c r="E42" t="s">
-        <v>24</v>
+        <v>172</v>
       </c>
       <c r="F42" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="G42" t="s">
         <v>107</v>
@@ -21587,34 +21587,34 @@
         <v>126</v>
       </c>
       <c r="I42" t="s">
-        <v>109</v>
+        <v>220</v>
       </c>
       <c r="J42">
-        <v>1852</v>
+        <v>1951</v>
       </c>
       <c r="K42">
-        <v>174</v>
+        <v>75</v>
       </c>
       <c r="L42">
-        <v>205000</v>
+        <v>457835</v>
       </c>
       <c r="M42">
-        <v>262.24</v>
+        <v>361.05</v>
       </c>
       <c r="N42">
-        <v>0.26224000000000003</v>
+        <v>0.36105000000000004</v>
       </c>
       <c r="O42">
-        <v>84.74</v>
+        <v>105.69</v>
       </c>
       <c r="P42">
-        <v>30.5</v>
+        <v>43.65</v>
       </c>
       <c r="Q42" s="10">
         <v>46265</v>
       </c>
       <c r="R42" t="s">
-        <v>374</v>
+        <v>265</v>
       </c>
       <c r="S42" t="s">
         <v>30</v>
@@ -21625,19 +21625,19 @@
     </row>
     <row r="43" spans="1:20">
       <c r="A43">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>397</v>
+        <v>267</v>
       </c>
       <c r="C43" t="s">
-        <v>398</v>
+        <v>268</v>
       </c>
       <c r="D43" t="s">
-        <v>398</v>
+        <v>269</v>
       </c>
       <c r="E43" t="s">
-        <v>387</v>
+        <v>270</v>
       </c>
       <c r="F43" t="s">
         <v>160</v>
@@ -21646,37 +21646,37 @@
         <v>26</v>
       </c>
       <c r="H43" t="s">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="I43" t="s">
-        <v>399</v>
+        <v>271</v>
       </c>
       <c r="J43">
-        <v>1972</v>
+        <v>1896</v>
       </c>
       <c r="K43">
-        <v>54</v>
+        <v>130</v>
       </c>
       <c r="L43">
-        <v>111397</v>
+        <v>112774</v>
       </c>
       <c r="M43">
-        <v>256.11</v>
+        <v>355.34</v>
       </c>
       <c r="N43">
-        <v>0.25611</v>
+        <v>0.35533999999999999</v>
       </c>
       <c r="O43">
-        <v>43.72</v>
+        <v>76.09</v>
       </c>
       <c r="P43">
-        <v>29.59</v>
+        <v>26.780000000000005</v>
       </c>
       <c r="Q43" s="10">
         <v>46265</v>
       </c>
       <c r="R43" t="s">
-        <v>400</v>
+        <v>272</v>
       </c>
       <c r="S43" t="s">
         <v>30</v>
@@ -21687,22 +21687,22 @@
     </row>
     <row r="44" spans="1:20">
       <c r="A44">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>578</v>
+        <v>274</v>
       </c>
       <c r="C44" t="s">
-        <v>579</v>
+        <v>275</v>
       </c>
       <c r="D44" t="s">
-        <v>580</v>
+        <v>275</v>
       </c>
       <c r="E44" t="s">
-        <v>363</v>
+        <v>276</v>
       </c>
       <c r="F44" t="s">
-        <v>25</v>
+        <v>160</v>
       </c>
       <c r="G44" t="s">
         <v>107</v>
@@ -21711,34 +21711,34 @@
         <v>126</v>
       </c>
       <c r="I44" t="s">
-        <v>364</v>
+        <v>277</v>
       </c>
       <c r="J44">
-        <v>1855</v>
+        <v>1865</v>
       </c>
       <c r="K44">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="L44">
-        <v>94867</v>
+        <v>211479</v>
       </c>
       <c r="M44">
-        <v>198.02</v>
+        <v>352.76</v>
       </c>
       <c r="N44">
-        <v>0.19802</v>
+        <v>0.35276000000000002</v>
       </c>
       <c r="O44">
-        <v>46.37</v>
+        <v>72.400000000000006</v>
       </c>
       <c r="P44">
-        <v>29.100000000000005</v>
+        <v>41.15</v>
       </c>
       <c r="Q44" s="10">
         <v>46265</v>
       </c>
       <c r="R44" t="s">
-        <v>581</v>
+        <v>278</v>
       </c>
       <c r="S44" t="s">
         <v>30</v>
@@ -21749,16 +21749,16 @@
     </row>
     <row r="45" spans="1:20">
       <c r="A45">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>212</v>
+        <v>280</v>
       </c>
       <c r="C45" t="s">
-        <v>213</v>
+        <v>281</v>
       </c>
       <c r="D45" t="s">
-        <v>214</v>
+        <v>282</v>
       </c>
       <c r="E45" t="s">
         <v>24</v>
@@ -21767,10 +21767,10 @@
         <v>25</v>
       </c>
       <c r="G45" t="s">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="H45" t="s">
-        <v>36</v>
+        <v>283</v>
       </c>
       <c r="I45" t="s">
         <v>109</v>
@@ -21782,25 +21782,25 @@
         <v>49</v>
       </c>
       <c r="L45">
-        <v>141000</v>
+        <v>390000</v>
       </c>
       <c r="M45">
-        <v>431.29</v>
+        <v>349.97</v>
       </c>
       <c r="N45">
-        <v>0.43129000000000001</v>
+        <v>0.34997</v>
       </c>
       <c r="O45">
-        <v>67.349999999999994</v>
+        <v>449.71</v>
       </c>
       <c r="P45">
-        <v>29.03</v>
+        <v>3.2300000000000004</v>
       </c>
       <c r="Q45" s="10">
         <v>46265</v>
       </c>
       <c r="R45" t="s">
-        <v>215</v>
+        <v>284</v>
       </c>
       <c r="S45" t="s">
         <v>30</v>
@@ -21811,16 +21811,16 @@
     </row>
     <row r="46" spans="1:20">
       <c r="A46">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="C46" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="D46" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="E46" t="s">
         <v>24</v>
@@ -21829,40 +21829,40 @@
         <v>25</v>
       </c>
       <c r="G46" t="s">
-        <v>26</v>
+        <v>289</v>
       </c>
       <c r="H46" t="s">
-        <v>88</v>
+        <v>290</v>
       </c>
       <c r="I46" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="J46">
-        <v>1997</v>
+        <v>1892</v>
       </c>
       <c r="K46">
-        <v>29</v>
+        <v>134</v>
       </c>
       <c r="L46">
-        <v>16000</v>
+        <v>57000</v>
       </c>
       <c r="M46">
-        <v>338.75</v>
+        <v>348.6</v>
       </c>
       <c r="N46">
-        <v>0.33875</v>
+        <v>0.34860000000000002</v>
       </c>
       <c r="O46">
-        <v>46.88</v>
+        <v>50.63</v>
       </c>
       <c r="P46">
-        <v>28.15</v>
+        <v>21.8</v>
       </c>
       <c r="Q46" s="10">
         <v>46265</v>
       </c>
       <c r="R46" t="s">
-        <v>304</v>
+        <v>291</v>
       </c>
       <c r="S46" t="s">
         <v>30</v>
@@ -21873,58 +21873,58 @@
     </row>
     <row r="47" spans="1:20">
       <c r="A47">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B47" t="s">
-        <v>348</v>
+        <v>301</v>
       </c>
       <c r="C47" t="s">
-        <v>349</v>
+        <v>302</v>
       </c>
       <c r="D47" t="s">
-        <v>350</v>
+        <v>303</v>
       </c>
       <c r="E47" t="s">
-        <v>270</v>
+        <v>24</v>
       </c>
       <c r="F47" t="s">
-        <v>160</v>
+        <v>25</v>
       </c>
       <c r="G47" t="s">
         <v>26</v>
       </c>
       <c r="H47" t="s">
-        <v>120</v>
+        <v>88</v>
       </c>
       <c r="I47" t="s">
-        <v>351</v>
+        <v>28</v>
       </c>
       <c r="J47">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="K47">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L47">
-        <v>75267</v>
+        <v>16000</v>
       </c>
       <c r="M47">
-        <v>289.38</v>
+        <v>338.75</v>
       </c>
       <c r="N47">
-        <v>0.28937999999999997</v>
+        <v>0.33875</v>
       </c>
       <c r="O47">
-        <v>56.57</v>
+        <v>46.88</v>
       </c>
       <c r="P47">
-        <v>27.889999999999997</v>
+        <v>28.15</v>
       </c>
       <c r="Q47" s="10">
         <v>46265</v>
       </c>
       <c r="R47" t="s">
-        <v>352</v>
+        <v>304</v>
       </c>
       <c r="S47" t="s">
         <v>30</v>
@@ -21935,58 +21935,58 @@
     </row>
     <row r="48" spans="1:20">
       <c r="A48">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B48" t="s">
-        <v>267</v>
+        <v>306</v>
       </c>
       <c r="C48" t="s">
-        <v>268</v>
+        <v>307</v>
       </c>
       <c r="D48" t="s">
-        <v>269</v>
+        <v>308</v>
       </c>
       <c r="E48" t="s">
-        <v>270</v>
+        <v>24</v>
       </c>
       <c r="F48" t="s">
-        <v>160</v>
+        <v>25</v>
       </c>
       <c r="G48" t="s">
-        <v>26</v>
+        <v>138</v>
       </c>
       <c r="H48" t="s">
-        <v>120</v>
+        <v>309</v>
       </c>
       <c r="I48" t="s">
-        <v>271</v>
+        <v>109</v>
       </c>
       <c r="J48">
-        <v>1896</v>
+        <v>1837</v>
       </c>
       <c r="K48">
-        <v>130</v>
+        <v>189</v>
       </c>
       <c r="L48">
-        <v>112774</v>
+        <v>104000</v>
       </c>
       <c r="M48">
-        <v>355.34</v>
+        <v>338.11</v>
       </c>
       <c r="N48">
-        <v>0.35533999999999999</v>
+        <v>0.33811000000000002</v>
       </c>
       <c r="O48">
-        <v>76.09</v>
+        <v>86.71</v>
       </c>
       <c r="P48">
-        <v>26.780000000000005</v>
+        <v>23.92</v>
       </c>
       <c r="Q48" s="10">
         <v>46265</v>
       </c>
       <c r="R48" t="s">
-        <v>272</v>
+        <v>310</v>
       </c>
       <c r="S48" t="s">
         <v>30</v>
@@ -21997,58 +21997,58 @@
     </row>
     <row r="49" spans="1:20">
       <c r="A49">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="B49" t="s">
-        <v>501</v>
+        <v>312</v>
       </c>
       <c r="C49" t="s">
-        <v>502</v>
+        <v>313</v>
       </c>
       <c r="D49" t="s">
-        <v>503</v>
+        <v>314</v>
       </c>
       <c r="E49" t="s">
-        <v>276</v>
+        <v>24</v>
       </c>
       <c r="F49" t="s">
-        <v>160</v>
+        <v>25</v>
       </c>
       <c r="G49" t="s">
-        <v>449</v>
+        <v>107</v>
       </c>
       <c r="H49" t="s">
-        <v>504</v>
+        <v>126</v>
       </c>
       <c r="I49" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="J49">
-        <v>1879</v>
+        <v>1935</v>
       </c>
       <c r="K49">
-        <v>147</v>
+        <v>91</v>
       </c>
       <c r="L49">
-        <v>65177</v>
+        <v>83000</v>
       </c>
       <c r="M49">
-        <v>225.3</v>
+        <v>335.23</v>
       </c>
       <c r="N49">
-        <v>0.2253</v>
+        <v>0.33523000000000003</v>
       </c>
       <c r="O49">
-        <v>34.65</v>
+        <v>68.77</v>
       </c>
       <c r="P49">
-        <v>26.170000000000005</v>
+        <v>34.049999999999997</v>
       </c>
       <c r="Q49" s="10">
         <v>46265</v>
       </c>
       <c r="R49" t="s">
-        <v>505</v>
+        <v>315</v>
       </c>
       <c r="S49" t="s">
         <v>30</v>
@@ -22059,16 +22059,16 @@
     </row>
     <row r="50" spans="1:20">
       <c r="A50">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="B50" t="s">
-        <v>112</v>
+        <v>317</v>
       </c>
       <c r="C50" t="s">
-        <v>113</v>
+        <v>318</v>
       </c>
       <c r="D50" t="s">
-        <v>114</v>
+        <v>319</v>
       </c>
       <c r="E50" t="s">
         <v>24</v>
@@ -22077,13 +22077,13 @@
         <v>25</v>
       </c>
       <c r="G50" t="s">
-        <v>26</v>
+        <v>138</v>
       </c>
       <c r="H50" t="s">
-        <v>27</v>
+        <v>139</v>
       </c>
       <c r="I50" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="J50">
         <v>1978</v>
@@ -22092,25 +22092,25 @@
         <v>48</v>
       </c>
       <c r="L50">
-        <v>53000</v>
+        <v>472400</v>
       </c>
       <c r="M50">
-        <v>1066</v>
+        <v>327.26</v>
       </c>
       <c r="N50">
-        <v>1.0660000000000001</v>
+        <v>0.32726</v>
       </c>
       <c r="O50">
-        <v>90.27</v>
+        <v>166.59</v>
       </c>
       <c r="P50">
-        <v>25.82</v>
+        <v>11.29</v>
       </c>
       <c r="Q50" s="10">
         <v>46265</v>
       </c>
       <c r="R50" t="s">
-        <v>115</v>
+        <v>320</v>
       </c>
       <c r="S50" t="s">
         <v>30</v>
@@ -22121,58 +22121,58 @@
     </row>
     <row r="51" spans="1:20">
       <c r="A51">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B51" t="s">
-        <v>97</v>
+        <v>322</v>
       </c>
       <c r="C51" t="s">
-        <v>98</v>
+        <v>323</v>
       </c>
       <c r="D51" t="s">
-        <v>99</v>
+        <v>324</v>
       </c>
       <c r="E51" t="s">
-        <v>100</v>
+        <v>172</v>
       </c>
       <c r="F51" t="s">
         <v>59</v>
       </c>
       <c r="G51" t="s">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="H51" t="s">
-        <v>27</v>
+        <v>126</v>
       </c>
       <c r="I51" t="s">
-        <v>101</v>
+        <v>220</v>
       </c>
       <c r="J51">
-        <v>1969</v>
+        <v>1912</v>
       </c>
       <c r="K51">
-        <v>57</v>
+        <v>114</v>
       </c>
       <c r="L51">
-        <v>259149</v>
+        <v>0</v>
       </c>
       <c r="M51">
-        <v>1248</v>
+        <v>312.18</v>
       </c>
       <c r="N51">
-        <v>1.248</v>
+        <v>0.31218000000000001</v>
       </c>
       <c r="O51">
-        <v>270.94</v>
+        <v>95.37</v>
       </c>
       <c r="P51">
-        <v>25.53</v>
+        <v>45.09</v>
       </c>
       <c r="Q51" s="10">
         <v>46265</v>
       </c>
       <c r="R51" t="s">
-        <v>102</v>
+        <v>325</v>
       </c>
       <c r="S51" t="s">
         <v>30</v>
@@ -22183,16 +22183,16 @@
     </row>
     <row r="52" spans="1:20">
       <c r="A52">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="B52" t="s">
-        <v>524</v>
+        <v>327</v>
       </c>
       <c r="C52" t="s">
-        <v>525</v>
+        <v>328</v>
       </c>
       <c r="D52" t="s">
-        <v>526</v>
+        <v>329</v>
       </c>
       <c r="E52" t="s">
         <v>24</v>
@@ -22201,40 +22201,40 @@
         <v>25</v>
       </c>
       <c r="G52" t="s">
-        <v>107</v>
+        <v>26</v>
       </c>
       <c r="H52" t="s">
-        <v>126</v>
+        <v>36</v>
       </c>
       <c r="I52" t="s">
-        <v>109</v>
+        <v>28</v>
       </c>
       <c r="J52">
-        <v>1812</v>
+        <v>2005</v>
       </c>
       <c r="K52">
-        <v>214</v>
+        <v>21</v>
       </c>
       <c r="L52">
-        <v>226000</v>
+        <v>16068</v>
       </c>
       <c r="M52">
-        <v>220.71</v>
+        <v>310.83999999999997</v>
       </c>
       <c r="N52">
-        <v>0.22071000000000002</v>
+        <v>0.31083999999999995</v>
       </c>
       <c r="O52">
-        <v>88.08</v>
+        <v>10.6</v>
       </c>
       <c r="P52">
-        <v>24.85</v>
+        <v>13.170000000000002</v>
       </c>
       <c r="Q52" s="10">
         <v>46265</v>
       </c>
       <c r="R52" t="s">
-        <v>527</v>
+        <v>330</v>
       </c>
       <c r="S52" t="s">
         <v>30</v>
@@ -22245,16 +22245,16 @@
     </row>
     <row r="53" spans="1:20">
       <c r="A53">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="B53" t="s">
-        <v>485</v>
+        <v>332</v>
       </c>
       <c r="C53" t="s">
-        <v>486</v>
+        <v>333</v>
       </c>
       <c r="D53" t="s">
-        <v>487</v>
+        <v>334</v>
       </c>
       <c r="E53" t="s">
         <v>24</v>
@@ -22266,37 +22266,37 @@
         <v>26</v>
       </c>
       <c r="H53" t="s">
-        <v>120</v>
+        <v>66</v>
       </c>
       <c r="I53" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="J53">
-        <v>1980</v>
+        <v>1984</v>
       </c>
       <c r="K53">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="L53">
-        <v>31500</v>
+        <v>97000</v>
       </c>
       <c r="M53">
-        <v>232.49</v>
+        <v>300.17</v>
       </c>
       <c r="N53">
-        <v>0.23249</v>
+        <v>0.30016999999999999</v>
       </c>
       <c r="O53">
-        <v>37.22</v>
+        <v>134</v>
       </c>
       <c r="P53">
-        <v>24.41</v>
+        <v>8.75</v>
       </c>
       <c r="Q53" s="10">
         <v>46265</v>
       </c>
       <c r="R53" t="s">
-        <v>488</v>
+        <v>335</v>
       </c>
       <c r="S53" t="s">
         <v>30</v>
@@ -22307,16 +22307,16 @@
     </row>
     <row r="54" spans="1:20">
       <c r="A54">
-        <v>97</v>
+        <v>54</v>
       </c>
       <c r="B54" t="s">
-        <v>589</v>
+        <v>337</v>
       </c>
       <c r="C54" t="s">
-        <v>590</v>
+        <v>338</v>
       </c>
       <c r="D54" t="s">
-        <v>591</v>
+        <v>339</v>
       </c>
       <c r="E54" t="s">
         <v>24</v>
@@ -22325,43 +22325,43 @@
         <v>25</v>
       </c>
       <c r="G54" t="s">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="H54" t="s">
-        <v>592</v>
+        <v>126</v>
       </c>
       <c r="I54" t="s">
         <v>109</v>
       </c>
       <c r="J54">
-        <v>1932</v>
+        <v>1869</v>
       </c>
       <c r="K54">
-        <v>94</v>
+        <v>157</v>
       </c>
       <c r="L54">
-        <v>170000</v>
+        <v>47400</v>
       </c>
       <c r="M54">
-        <v>196.62</v>
+        <v>298.99</v>
       </c>
       <c r="N54">
-        <v>0.19662000000000002</v>
+        <v>0.29899000000000003</v>
       </c>
       <c r="O54">
-        <v>23.1</v>
+        <v>60.44</v>
       </c>
       <c r="P54">
-        <v>24.25</v>
+        <v>37.53</v>
       </c>
       <c r="Q54" s="10">
         <v>46265</v>
       </c>
       <c r="R54" t="s">
-        <v>593</v>
+        <v>340</v>
       </c>
       <c r="S54" t="s">
-        <v>594</v>
+        <v>30</v>
       </c>
       <c r="T54" t="s">
         <v>31</v>
@@ -22369,16 +22369,16 @@
     </row>
     <row r="55" spans="1:20">
       <c r="A55">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="B55" t="s">
-        <v>542</v>
+        <v>342</v>
       </c>
       <c r="C55" t="s">
-        <v>543</v>
+        <v>343</v>
       </c>
       <c r="D55" t="s">
-        <v>544</v>
+        <v>344</v>
       </c>
       <c r="E55" t="s">
         <v>24</v>
@@ -22387,40 +22387,40 @@
         <v>25</v>
       </c>
       <c r="G55" t="s">
-        <v>26</v>
+        <v>236</v>
       </c>
       <c r="H55" t="s">
-        <v>36</v>
+        <v>345</v>
       </c>
       <c r="I55" t="s">
         <v>109</v>
       </c>
       <c r="J55">
-        <v>1999</v>
+        <v>2008</v>
       </c>
       <c r="K55">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="L55">
-        <v>83334</v>
+        <v>84900</v>
       </c>
       <c r="M55">
-        <v>213.84</v>
+        <v>293.05</v>
       </c>
       <c r="N55">
-        <v>0.21384</v>
+        <v>0.29305000000000003</v>
       </c>
       <c r="O55">
-        <v>42.82</v>
+        <v>41.49</v>
       </c>
       <c r="P55">
-        <v>23.97</v>
+        <v>34.14</v>
       </c>
       <c r="Q55" s="10">
         <v>46265</v>
       </c>
       <c r="R55" t="s">
-        <v>545</v>
+        <v>346</v>
       </c>
       <c r="S55" t="s">
         <v>30</v>
@@ -22431,58 +22431,58 @@
     </row>
     <row r="56" spans="1:20">
       <c r="A56">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B56" t="s">
-        <v>306</v>
+        <v>348</v>
       </c>
       <c r="C56" t="s">
-        <v>307</v>
+        <v>349</v>
       </c>
       <c r="D56" t="s">
-        <v>308</v>
+        <v>350</v>
       </c>
       <c r="E56" t="s">
-        <v>24</v>
+        <v>270</v>
       </c>
       <c r="F56" t="s">
-        <v>25</v>
+        <v>160</v>
       </c>
       <c r="G56" t="s">
-        <v>138</v>
+        <v>26</v>
       </c>
       <c r="H56" t="s">
-        <v>309</v>
+        <v>120</v>
       </c>
       <c r="I56" t="s">
-        <v>109</v>
+        <v>351</v>
       </c>
       <c r="J56">
-        <v>1837</v>
+        <v>1996</v>
       </c>
       <c r="K56">
-        <v>189</v>
+        <v>30</v>
       </c>
       <c r="L56">
-        <v>104000</v>
+        <v>75267</v>
       </c>
       <c r="M56">
-        <v>338.11</v>
+        <v>289.38</v>
       </c>
       <c r="N56">
-        <v>0.33811000000000002</v>
+        <v>0.28937999999999997</v>
       </c>
       <c r="O56">
-        <v>86.71</v>
+        <v>56.57</v>
       </c>
       <c r="P56">
-        <v>23.92</v>
+        <v>27.889999999999997</v>
       </c>
       <c r="Q56" s="10">
         <v>46265</v>
       </c>
       <c r="R56" t="s">
-        <v>310</v>
+        <v>352</v>
       </c>
       <c r="S56" t="s">
         <v>30</v>
@@ -22493,58 +22493,58 @@
     </row>
     <row r="57" spans="1:20">
       <c r="A57">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="B57" t="s">
-        <v>286</v>
+        <v>354</v>
       </c>
       <c r="C57" t="s">
-        <v>287</v>
+        <v>355</v>
       </c>
       <c r="D57" t="s">
-        <v>288</v>
+        <v>356</v>
       </c>
       <c r="E57" t="s">
-        <v>24</v>
+        <v>172</v>
       </c>
       <c r="F57" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="G57" t="s">
-        <v>289</v>
+        <v>26</v>
       </c>
       <c r="H57" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
       <c r="I57" t="s">
-        <v>109</v>
+        <v>357</v>
       </c>
       <c r="J57">
-        <v>1892</v>
+        <v>1999</v>
       </c>
       <c r="K57">
-        <v>134</v>
+        <v>27</v>
       </c>
       <c r="L57">
-        <v>57000</v>
+        <v>131462</v>
       </c>
       <c r="M57">
-        <v>348.6</v>
+        <v>283.60000000000002</v>
       </c>
       <c r="N57">
-        <v>0.34860000000000002</v>
+        <v>0.28360000000000002</v>
       </c>
       <c r="O57">
-        <v>50.63</v>
+        <v>145.38999999999999</v>
       </c>
       <c r="P57">
-        <v>21.8</v>
+        <v>13.56</v>
       </c>
       <c r="Q57" s="10">
         <v>46265</v>
       </c>
       <c r="R57" t="s">
-        <v>291</v>
+        <v>358</v>
       </c>
       <c r="S57" t="s">
         <v>30</v>
@@ -22555,58 +22555,58 @@
     </row>
     <row r="58" spans="1:20">
       <c r="A58">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="B58" t="s">
-        <v>426</v>
+        <v>360</v>
       </c>
       <c r="C58" t="s">
-        <v>427</v>
+        <v>361</v>
       </c>
       <c r="D58" t="s">
-        <v>428</v>
+        <v>362</v>
       </c>
       <c r="E58" t="s">
-        <v>172</v>
+        <v>363</v>
       </c>
       <c r="F58" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="G58" t="s">
-        <v>429</v>
+        <v>107</v>
       </c>
       <c r="H58" t="s">
-        <v>430</v>
+        <v>126</v>
       </c>
       <c r="I58" t="s">
-        <v>431</v>
+        <v>364</v>
       </c>
       <c r="J58">
-        <v>2011</v>
+        <v>1864</v>
       </c>
       <c r="K58">
-        <v>15</v>
+        <v>162</v>
       </c>
       <c r="L58">
-        <v>0</v>
+        <v>91427</v>
       </c>
       <c r="M58">
-        <v>250.33</v>
+        <v>282.16000000000003</v>
       </c>
       <c r="N58">
-        <v>0.25033</v>
+        <v>0.28216000000000002</v>
       </c>
       <c r="O58">
-        <v>63.65</v>
+        <v>50.53</v>
       </c>
       <c r="P58">
-        <v>21.64</v>
+        <v>40.590000000000003</v>
       </c>
       <c r="Q58" s="10">
         <v>46265</v>
       </c>
       <c r="R58" t="s">
-        <v>432</v>
+        <v>365</v>
       </c>
       <c r="S58" t="s">
         <v>30</v>
@@ -22617,58 +22617,58 @@
     </row>
     <row r="59" spans="1:20">
       <c r="A59">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="B59" t="s">
-        <v>409</v>
+        <v>367</v>
       </c>
       <c r="C59" t="s">
-        <v>410</v>
+        <v>368</v>
       </c>
       <c r="D59" t="s">
-        <v>411</v>
+        <v>368</v>
       </c>
       <c r="E59" t="s">
-        <v>276</v>
+        <v>24</v>
       </c>
       <c r="F59" t="s">
-        <v>160</v>
+        <v>25</v>
       </c>
       <c r="G59" t="s">
-        <v>26</v>
+        <v>289</v>
       </c>
       <c r="H59" t="s">
-        <v>120</v>
+        <v>290</v>
       </c>
       <c r="I59" t="s">
-        <v>412</v>
+        <v>109</v>
       </c>
       <c r="J59">
-        <v>1999</v>
+        <v>2020</v>
       </c>
       <c r="K59">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="L59">
-        <v>95100</v>
+        <v>180000</v>
       </c>
       <c r="M59">
-        <v>251.72</v>
+        <v>281.39999999999998</v>
       </c>
       <c r="N59">
-        <v>0.25172</v>
+        <v>0.28139999999999998</v>
       </c>
       <c r="O59">
-        <v>60.43</v>
+        <v>90.37</v>
       </c>
       <c r="P59">
-        <v>21.11</v>
+        <v>9.85</v>
       </c>
       <c r="Q59" s="10">
         <v>46265</v>
       </c>
       <c r="R59" t="s">
-        <v>413</v>
+        <v>369</v>
       </c>
       <c r="S59" t="s">
         <v>30</v>
@@ -22679,58 +22679,58 @@
     </row>
     <row r="60" spans="1:20">
       <c r="A60">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="B60" t="s">
-        <v>583</v>
+        <v>371</v>
       </c>
       <c r="C60" t="s">
-        <v>584</v>
+        <v>372</v>
       </c>
       <c r="D60" t="s">
-        <v>585</v>
+        <v>373</v>
       </c>
       <c r="E60" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="F60" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="G60" t="s">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="H60" t="s">
-        <v>27</v>
+        <v>126</v>
       </c>
       <c r="I60" t="s">
-        <v>586</v>
+        <v>109</v>
       </c>
       <c r="J60">
-        <v>1997</v>
+        <v>1852</v>
       </c>
       <c r="K60">
-        <v>29</v>
+        <v>174</v>
       </c>
       <c r="L60">
-        <v>0</v>
+        <v>205000</v>
       </c>
       <c r="M60">
-        <v>197.85</v>
+        <v>262.24</v>
       </c>
       <c r="N60">
-        <v>0.19785</v>
+        <v>0.26224000000000003</v>
       </c>
       <c r="O60">
-        <v>19.23</v>
+        <v>84.74</v>
       </c>
       <c r="P60">
-        <v>20.95</v>
+        <v>30.5</v>
       </c>
       <c r="Q60" s="10">
         <v>46265</v>
       </c>
       <c r="R60" t="s">
-        <v>587</v>
+        <v>374</v>
       </c>
       <c r="S60" t="s">
         <v>30</v>
@@ -22741,19 +22741,19 @@
     </row>
     <row r="61" spans="1:20">
       <c r="A61">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="B61" t="s">
-        <v>554</v>
+        <v>376</v>
       </c>
       <c r="C61" t="s">
-        <v>555</v>
+        <v>377</v>
       </c>
       <c r="D61" t="s">
-        <v>556</v>
+        <v>378</v>
       </c>
       <c r="E61" t="s">
-        <v>550</v>
+        <v>379</v>
       </c>
       <c r="F61" t="s">
         <v>160</v>
@@ -22765,34 +22765,34 @@
         <v>380</v>
       </c>
       <c r="I61" t="s">
-        <v>557</v>
+        <v>381</v>
       </c>
       <c r="J61">
-        <v>1985</v>
+        <v>1987</v>
       </c>
       <c r="K61">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L61">
-        <v>163000</v>
+        <v>211000</v>
       </c>
       <c r="M61">
-        <v>210.73</v>
+        <v>259.62</v>
       </c>
       <c r="N61">
-        <v>0.21073</v>
+        <v>0.25962000000000002</v>
       </c>
       <c r="O61">
-        <v>42.5</v>
+        <v>93.86</v>
       </c>
       <c r="P61">
-        <v>20.92</v>
+        <v>20.66</v>
       </c>
       <c r="Q61" s="10">
         <v>46265</v>
       </c>
       <c r="R61" t="s">
-        <v>558</v>
+        <v>382</v>
       </c>
       <c r="S61" t="s">
         <v>30</v>
@@ -22803,58 +22803,58 @@
     </row>
     <row r="62" spans="1:20">
       <c r="A62">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B62" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="C62" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="D62" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="E62" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="F62" t="s">
         <v>160</v>
       </c>
       <c r="G62" t="s">
-        <v>138</v>
+        <v>289</v>
       </c>
       <c r="H62" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="I62" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="J62">
-        <v>1987</v>
+        <v>1847</v>
       </c>
       <c r="K62">
-        <v>39</v>
+        <v>179</v>
       </c>
       <c r="L62">
-        <v>211000</v>
+        <v>318000</v>
       </c>
       <c r="M62">
-        <v>259.62</v>
+        <v>258.89999999999998</v>
       </c>
       <c r="N62">
-        <v>0.25962000000000002</v>
+        <v>0.25889999999999996</v>
       </c>
       <c r="O62">
-        <v>93.86</v>
+        <v>93.33</v>
       </c>
       <c r="P62">
-        <v>20.66</v>
+        <v>13.889999999999999</v>
       </c>
       <c r="Q62" s="10">
         <v>46265</v>
       </c>
       <c r="R62" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="S62" t="s">
         <v>30</v>
@@ -22865,58 +22865,58 @@
     </row>
     <row r="63" spans="1:20">
       <c r="A63">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="B63" t="s">
-        <v>202</v>
+        <v>392</v>
       </c>
       <c r="C63" t="s">
-        <v>203</v>
+        <v>393</v>
       </c>
       <c r="D63" t="s">
-        <v>204</v>
+        <v>394</v>
       </c>
       <c r="E63" t="s">
-        <v>24</v>
+        <v>276</v>
       </c>
       <c r="F63" t="s">
-        <v>25</v>
+        <v>160</v>
       </c>
       <c r="G63" t="s">
         <v>26</v>
       </c>
       <c r="H63" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="I63" t="s">
         <v>28</v>
       </c>
       <c r="J63">
-        <v>1984</v>
+        <v>1990</v>
       </c>
       <c r="K63">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="L63">
-        <v>86200</v>
+        <v>9584</v>
       </c>
       <c r="M63">
-        <v>436.49</v>
+        <v>257.83</v>
       </c>
       <c r="N63">
-        <v>0.43648999999999999</v>
+        <v>0.25783</v>
       </c>
       <c r="O63">
-        <v>60.74</v>
+        <v>4.92</v>
       </c>
       <c r="P63">
-        <v>19.59</v>
+        <v>18.45</v>
       </c>
       <c r="Q63" s="10">
         <v>46265</v>
       </c>
       <c r="R63" t="s">
-        <v>205</v>
+        <v>395</v>
       </c>
       <c r="S63" t="s">
         <v>30</v>
@@ -22927,58 +22927,58 @@
     </row>
     <row r="64" spans="1:20">
       <c r="A64">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B64" t="s">
-        <v>460</v>
+        <v>397</v>
       </c>
       <c r="C64" t="s">
-        <v>461</v>
+        <v>398</v>
       </c>
       <c r="D64" t="s">
-        <v>462</v>
+        <v>398</v>
       </c>
       <c r="E64" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="F64" t="s">
         <v>160</v>
       </c>
       <c r="G64" t="s">
-        <v>138</v>
+        <v>26</v>
       </c>
       <c r="H64" t="s">
-        <v>309</v>
+        <v>36</v>
       </c>
       <c r="I64" t="s">
-        <v>381</v>
+        <v>399</v>
       </c>
       <c r="J64">
-        <v>1909</v>
+        <v>1972</v>
       </c>
       <c r="K64">
-        <v>117</v>
+        <v>54</v>
       </c>
       <c r="L64">
-        <v>94610</v>
+        <v>111397</v>
       </c>
       <c r="M64">
-        <v>238.07</v>
+        <v>256.11</v>
       </c>
       <c r="N64">
-        <v>0.23807</v>
+        <v>0.25611</v>
       </c>
       <c r="O64">
-        <v>51.17</v>
+        <v>43.72</v>
       </c>
       <c r="P64">
-        <v>19.3</v>
+        <v>29.59</v>
       </c>
       <c r="Q64" s="10">
         <v>46265</v>
       </c>
       <c r="R64" t="s">
-        <v>463</v>
+        <v>400</v>
       </c>
       <c r="S64" t="s">
         <v>30</v>
@@ -22989,58 +22989,58 @@
     </row>
     <row r="65" spans="1:20">
       <c r="A65">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="B65" t="s">
-        <v>470</v>
+        <v>402</v>
       </c>
       <c r="C65" t="s">
-        <v>471</v>
+        <v>403</v>
       </c>
       <c r="D65" t="s">
-        <v>472</v>
+        <v>404</v>
       </c>
       <c r="E65" t="s">
-        <v>24</v>
+        <v>405</v>
       </c>
       <c r="F65" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="G65" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="H65" t="s">
-        <v>430</v>
+        <v>126</v>
       </c>
       <c r="I65" t="s">
-        <v>109</v>
+        <v>406</v>
       </c>
       <c r="J65">
-        <v>2024</v>
+        <v>2005</v>
       </c>
       <c r="K65">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="L65">
-        <v>78000</v>
+        <v>156000</v>
       </c>
       <c r="M65">
-        <v>237.35</v>
+        <v>255.87</v>
       </c>
       <c r="N65">
-        <v>0.23735000000000001</v>
+        <v>0.25586999999999999</v>
       </c>
       <c r="O65">
-        <v>39.369999999999997</v>
+        <v>49.47</v>
       </c>
       <c r="P65">
-        <v>19.29</v>
+        <v>44.37</v>
       </c>
       <c r="Q65" s="10">
         <v>46265</v>
       </c>
       <c r="R65" t="s">
-        <v>473</v>
+        <v>407</v>
       </c>
       <c r="S65" t="s">
         <v>30</v>
@@ -23051,58 +23051,58 @@
     </row>
     <row r="66" spans="1:20">
       <c r="A66">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="B66" t="s">
-        <v>507</v>
+        <v>409</v>
       </c>
       <c r="C66" t="s">
-        <v>508</v>
+        <v>410</v>
       </c>
       <c r="D66" t="s">
-        <v>509</v>
+        <v>411</v>
       </c>
       <c r="E66" t="s">
-        <v>24</v>
+        <v>276</v>
       </c>
       <c r="F66" t="s">
-        <v>25</v>
+        <v>160</v>
       </c>
       <c r="G66" t="s">
-        <v>107</v>
+        <v>26</v>
       </c>
       <c r="H66" t="s">
-        <v>149</v>
+        <v>120</v>
       </c>
       <c r="I66" t="s">
-        <v>109</v>
+        <v>412</v>
       </c>
       <c r="J66">
-        <v>1850</v>
+        <v>1999</v>
       </c>
       <c r="K66">
-        <v>176</v>
+        <v>27</v>
       </c>
       <c r="L66">
-        <v>76800</v>
+        <v>95100</v>
       </c>
       <c r="M66">
-        <v>223.55</v>
+        <v>251.72</v>
       </c>
       <c r="N66">
-        <v>0.22355</v>
+        <v>0.25172</v>
       </c>
       <c r="O66">
-        <v>74.17</v>
+        <v>60.43</v>
       </c>
       <c r="P66">
-        <v>19.2</v>
+        <v>21.11</v>
       </c>
       <c r="Q66" s="10">
         <v>46265</v>
       </c>
       <c r="R66" t="s">
-        <v>510</v>
+        <v>413</v>
       </c>
       <c r="S66" t="s">
         <v>30</v>
@@ -23113,16 +23113,16 @@
     </row>
     <row r="67" spans="1:20">
       <c r="A67">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B67" t="s">
-        <v>392</v>
+        <v>415</v>
       </c>
       <c r="C67" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="D67" t="s">
-        <v>394</v>
+        <v>417</v>
       </c>
       <c r="E67" t="s">
         <v>276</v>
@@ -23131,40 +23131,40 @@
         <v>160</v>
       </c>
       <c r="G67" t="s">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="H67" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="I67" t="s">
-        <v>28</v>
+        <v>277</v>
       </c>
       <c r="J67">
-        <v>1990</v>
+        <v>1907</v>
       </c>
       <c r="K67">
-        <v>36</v>
+        <v>119</v>
       </c>
       <c r="L67">
-        <v>9584</v>
+        <v>85000</v>
       </c>
       <c r="M67">
-        <v>257.83</v>
+        <v>251.71</v>
       </c>
       <c r="N67">
-        <v>0.25783</v>
+        <v>0.25170999999999999</v>
       </c>
       <c r="O67">
-        <v>4.92</v>
+        <v>267.33999999999997</v>
       </c>
       <c r="P67">
-        <v>18.45</v>
+        <v>11.26</v>
       </c>
       <c r="Q67" s="10">
         <v>46265</v>
       </c>
       <c r="R67" t="s">
-        <v>395</v>
+        <v>418</v>
       </c>
       <c r="S67" t="s">
         <v>30</v>
@@ -23175,58 +23175,58 @@
     </row>
     <row r="68" spans="1:20">
       <c r="A68">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="B68" t="s">
-        <v>245</v>
+        <v>420</v>
       </c>
       <c r="C68" t="s">
-        <v>246</v>
+        <v>421</v>
       </c>
       <c r="D68" t="s">
-        <v>247</v>
+        <v>422</v>
       </c>
       <c r="E68" t="s">
-        <v>24</v>
+        <v>270</v>
       </c>
       <c r="F68" t="s">
-        <v>25</v>
+        <v>160</v>
       </c>
       <c r="G68" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="H68" t="s">
-        <v>249</v>
+        <v>423</v>
       </c>
       <c r="I68" t="s">
-        <v>109</v>
+        <v>271</v>
       </c>
       <c r="J68">
-        <v>1925</v>
+        <v>1866</v>
       </c>
       <c r="K68">
-        <v>101</v>
+        <v>160</v>
       </c>
       <c r="L68">
-        <v>118000</v>
+        <v>271000</v>
       </c>
       <c r="M68">
-        <v>365.84</v>
+        <v>250.88</v>
       </c>
       <c r="N68">
-        <v>0.36584</v>
+        <v>0.25087999999999999</v>
       </c>
       <c r="O68">
-        <v>70.75</v>
+        <v>110.73</v>
       </c>
       <c r="P68">
-        <v>17.07</v>
+        <v>11.96</v>
       </c>
       <c r="Q68" s="10">
         <v>46265</v>
       </c>
       <c r="R68" t="s">
-        <v>250</v>
+        <v>424</v>
       </c>
       <c r="S68" t="s">
         <v>30</v>
@@ -23237,58 +23237,58 @@
     </row>
     <row r="69" spans="1:20">
       <c r="A69">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="B69" t="s">
-        <v>560</v>
+        <v>426</v>
       </c>
       <c r="C69" t="s">
-        <v>561</v>
+        <v>427</v>
       </c>
       <c r="D69" t="s">
-        <v>562</v>
+        <v>428</v>
       </c>
       <c r="E69" t="s">
-        <v>24</v>
+        <v>172</v>
       </c>
       <c r="F69" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="G69" t="s">
-        <v>532</v>
+        <v>429</v>
       </c>
       <c r="H69" t="s">
-        <v>533</v>
+        <v>430</v>
       </c>
       <c r="I69" t="s">
-        <v>109</v>
+        <v>431</v>
       </c>
       <c r="J69">
-        <v>2000</v>
+        <v>2011</v>
       </c>
       <c r="K69">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="L69">
-        <v>89900</v>
+        <v>0</v>
       </c>
       <c r="M69">
-        <v>208.51</v>
+        <v>250.33</v>
       </c>
       <c r="N69">
-        <v>0.20851</v>
+        <v>0.25033</v>
       </c>
       <c r="O69">
-        <v>139.13999999999999</v>
+        <v>63.65</v>
       </c>
       <c r="P69">
-        <v>16.510000000000002</v>
+        <v>21.64</v>
       </c>
       <c r="Q69" s="10">
         <v>46265</v>
       </c>
       <c r="R69" t="s">
-        <v>563</v>
+        <v>432</v>
       </c>
       <c r="S69" t="s">
         <v>30</v>
@@ -23299,16 +23299,16 @@
     </row>
     <row r="70" spans="1:20">
       <c r="A70">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B70" t="s">
-        <v>490</v>
+        <v>434</v>
       </c>
       <c r="C70" t="s">
-        <v>491</v>
+        <v>435</v>
       </c>
       <c r="D70" t="s">
-        <v>492</v>
+        <v>436</v>
       </c>
       <c r="E70" t="s">
         <v>24</v>
@@ -23320,37 +23320,37 @@
         <v>26</v>
       </c>
       <c r="H70" t="s">
-        <v>493</v>
+        <v>66</v>
       </c>
       <c r="I70" t="s">
         <v>109</v>
       </c>
       <c r="J70">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="K70">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L70">
-        <v>125000</v>
+        <v>5115</v>
       </c>
       <c r="M70">
-        <v>229.2</v>
+        <v>247.84</v>
       </c>
       <c r="N70">
-        <v>0.22919999999999999</v>
+        <v>0.24784</v>
       </c>
       <c r="O70">
-        <v>45.19</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="P70">
-        <v>16.420000000000002</v>
+        <v>47.02</v>
       </c>
       <c r="Q70" s="10">
         <v>46265</v>
       </c>
       <c r="R70" t="s">
-        <v>494</v>
+        <v>437</v>
       </c>
       <c r="S70" t="s">
         <v>30</v>
@@ -23361,61 +23361,61 @@
     </row>
     <row r="71" spans="1:20">
       <c r="A71">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="B71" t="s">
-        <v>608</v>
+        <v>439</v>
       </c>
       <c r="C71" t="s">
-        <v>609</v>
+        <v>440</v>
       </c>
       <c r="D71" t="s">
-        <v>610</v>
+        <v>441</v>
       </c>
       <c r="E71" t="s">
-        <v>24</v>
+        <v>172</v>
       </c>
       <c r="F71" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="G71" t="s">
-        <v>532</v>
+        <v>236</v>
       </c>
       <c r="H71" t="s">
-        <v>533</v>
+        <v>442</v>
       </c>
       <c r="I71" t="s">
-        <v>28</v>
+        <v>173</v>
       </c>
       <c r="J71">
-        <v>1994</v>
+        <v>1999</v>
       </c>
       <c r="K71">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="L71">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="M71">
-        <v>194.29</v>
+        <v>242.18</v>
       </c>
       <c r="N71">
-        <v>0.19428999999999999</v>
+        <v>0.24218000000000001</v>
       </c>
       <c r="O71">
-        <v>88.308999999999997</v>
+        <v>26.44</v>
       </c>
       <c r="P71">
-        <v>16.170000000000002</v>
+        <v>67.239999999999995</v>
       </c>
       <c r="Q71" s="10">
         <v>46265</v>
       </c>
       <c r="R71" t="s">
-        <v>593</v>
+        <v>443</v>
       </c>
       <c r="S71" t="s">
-        <v>611</v>
+        <v>30</v>
       </c>
       <c r="T71" t="s">
         <v>31</v>
@@ -23423,58 +23423,58 @@
     </row>
     <row r="72" spans="1:20">
       <c r="A72">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="B72" t="s">
-        <v>104</v>
+        <v>445</v>
       </c>
       <c r="C72" t="s">
-        <v>105</v>
+        <v>446</v>
       </c>
       <c r="D72" t="s">
-        <v>106</v>
+        <v>447</v>
       </c>
       <c r="E72" t="s">
-        <v>24</v>
+        <v>448</v>
       </c>
       <c r="F72" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="G72" t="s">
-        <v>107</v>
+        <v>449</v>
       </c>
       <c r="H72" t="s">
-        <v>108</v>
+        <v>450</v>
       </c>
       <c r="I72" t="s">
-        <v>109</v>
+        <v>451</v>
       </c>
       <c r="J72">
-        <v>1839</v>
+        <v>1885</v>
       </c>
       <c r="K72">
-        <v>187</v>
+        <v>141</v>
       </c>
       <c r="L72">
-        <v>387800</v>
+        <v>0</v>
       </c>
       <c r="M72">
-        <v>1078</v>
+        <v>238.54</v>
       </c>
       <c r="N72">
-        <v>1.0780000000000001</v>
+        <v>0.23854</v>
       </c>
       <c r="O72">
-        <v>385.68</v>
+        <v>58.76</v>
       </c>
       <c r="P72">
-        <v>16.010000000000002</v>
+        <v>39.450000000000003</v>
       </c>
       <c r="Q72" s="10">
         <v>46265</v>
       </c>
       <c r="R72" t="s">
-        <v>110</v>
+        <v>453</v>
       </c>
       <c r="S72" t="s">
         <v>30</v>
@@ -23485,16 +23485,16 @@
     </row>
     <row r="73" spans="1:20">
       <c r="A73">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="B73" t="s">
-        <v>512</v>
+        <v>455</v>
       </c>
       <c r="C73" t="s">
-        <v>513</v>
+        <v>456</v>
       </c>
       <c r="D73" t="s">
-        <v>513</v>
+        <v>457</v>
       </c>
       <c r="E73" t="s">
         <v>24</v>
@@ -23506,37 +23506,37 @@
         <v>26</v>
       </c>
       <c r="H73" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="I73" t="s">
-        <v>109</v>
+        <v>28</v>
       </c>
       <c r="J73">
-        <v>1911</v>
+        <v>1930</v>
       </c>
       <c r="K73">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="L73">
-        <v>264300</v>
+        <v>33000</v>
       </c>
       <c r="M73">
-        <v>221.32</v>
+        <v>238.28</v>
       </c>
       <c r="N73">
-        <v>0.22131999999999999</v>
+        <v>0.23827999999999999</v>
       </c>
       <c r="O73">
-        <v>68.91</v>
+        <v>18.43</v>
       </c>
       <c r="P73">
-        <v>15.310000000000002</v>
+        <v>32.29</v>
       </c>
       <c r="Q73" s="10">
         <v>46265</v>
       </c>
       <c r="R73" t="s">
-        <v>514</v>
+        <v>458</v>
       </c>
       <c r="S73" t="s">
         <v>30</v>
@@ -23547,58 +23547,58 @@
     </row>
     <row r="74" spans="1:20">
       <c r="A74">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="B74" t="s">
-        <v>384</v>
+        <v>460</v>
       </c>
       <c r="C74" t="s">
-        <v>385</v>
+        <v>461</v>
       </c>
       <c r="D74" t="s">
-        <v>386</v>
+        <v>462</v>
       </c>
       <c r="E74" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="F74" t="s">
         <v>160</v>
       </c>
       <c r="G74" t="s">
-        <v>289</v>
+        <v>138</v>
       </c>
       <c r="H74" t="s">
-        <v>388</v>
+        <v>309</v>
       </c>
       <c r="I74" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="J74">
-        <v>1847</v>
+        <v>1909</v>
       </c>
       <c r="K74">
-        <v>179</v>
+        <v>117</v>
       </c>
       <c r="L74">
-        <v>318000</v>
+        <v>94610</v>
       </c>
       <c r="M74">
-        <v>258.89999999999998</v>
+        <v>238.07</v>
       </c>
       <c r="N74">
-        <v>0.25889999999999996</v>
+        <v>0.23807</v>
       </c>
       <c r="O74">
-        <v>93.33</v>
+        <v>51.17</v>
       </c>
       <c r="P74">
-        <v>13.889999999999999</v>
+        <v>19.3</v>
       </c>
       <c r="Q74" s="10">
         <v>46265</v>
       </c>
       <c r="R74" t="s">
-        <v>390</v>
+        <v>463</v>
       </c>
       <c r="S74" t="s">
         <v>30</v>
@@ -23609,16 +23609,16 @@
     </row>
     <row r="75" spans="1:20">
       <c r="A75">
-        <v>5</v>
+        <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>49</v>
+        <v>470</v>
       </c>
       <c r="C75" t="s">
-        <v>50</v>
+        <v>471</v>
       </c>
       <c r="D75" t="s">
-        <v>51</v>
+        <v>472</v>
       </c>
       <c r="E75" t="s">
         <v>24</v>
@@ -23627,40 +23627,40 @@
         <v>25</v>
       </c>
       <c r="G75" t="s">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="H75" t="s">
-        <v>52</v>
+        <v>430</v>
       </c>
       <c r="I75" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="J75">
-        <v>1994</v>
+        <v>2024</v>
       </c>
       <c r="K75">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="L75">
-        <v>1576000</v>
+        <v>78000</v>
       </c>
       <c r="M75">
-        <v>2794</v>
+        <v>237.35</v>
       </c>
       <c r="N75">
-        <v>2.794</v>
+        <v>0.23735000000000001</v>
       </c>
       <c r="O75">
-        <v>742.77</v>
+        <v>39.369999999999997</v>
       </c>
       <c r="P75">
-        <v>13.570000000000002</v>
+        <v>19.29</v>
       </c>
       <c r="Q75" s="10">
         <v>46265</v>
       </c>
       <c r="R75" t="s">
-        <v>53</v>
+        <v>473</v>
       </c>
       <c r="S75" t="s">
         <v>30</v>
@@ -23671,58 +23671,58 @@
     </row>
     <row r="76" spans="1:20">
       <c r="A76">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>354</v>
+        <v>475</v>
       </c>
       <c r="C76" t="s">
-        <v>355</v>
+        <v>476</v>
       </c>
       <c r="D76" t="s">
-        <v>356</v>
+        <v>477</v>
       </c>
       <c r="E76" t="s">
-        <v>172</v>
+        <v>24</v>
       </c>
       <c r="F76" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="G76" t="s">
         <v>26</v>
       </c>
       <c r="H76" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="I76" t="s">
-        <v>357</v>
+        <v>28</v>
       </c>
       <c r="J76">
-        <v>1999</v>
+        <v>2011</v>
       </c>
       <c r="K76">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="L76">
-        <v>131462</v>
+        <v>10698</v>
       </c>
       <c r="M76">
-        <v>283.60000000000002</v>
+        <v>236.01</v>
       </c>
       <c r="N76">
-        <v>0.28360000000000002</v>
+        <v>0.23601</v>
       </c>
       <c r="O76">
-        <v>145.38999999999999</v>
+        <v>5.09</v>
       </c>
       <c r="P76">
-        <v>13.56</v>
+        <v>0.03</v>
       </c>
       <c r="Q76" s="10">
         <v>46265</v>
       </c>
       <c r="R76" t="s">
-        <v>358</v>
+        <v>478</v>
       </c>
       <c r="S76" t="s">
         <v>30</v>
@@ -23733,58 +23733,58 @@
     </row>
     <row r="77" spans="1:20">
       <c r="A77">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>327</v>
+        <v>480</v>
       </c>
       <c r="C77" t="s">
-        <v>328</v>
+        <v>481</v>
       </c>
       <c r="D77" t="s">
-        <v>329</v>
+        <v>482</v>
       </c>
       <c r="E77" t="s">
-        <v>24</v>
+        <v>405</v>
       </c>
       <c r="F77" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="G77" t="s">
-        <v>26</v>
+        <v>248</v>
       </c>
       <c r="H77" t="s">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="I77" t="s">
-        <v>28</v>
+        <v>406</v>
       </c>
       <c r="J77">
-        <v>2005</v>
+        <v>1937</v>
       </c>
       <c r="K77">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="L77">
-        <v>16068</v>
+        <v>390927</v>
       </c>
       <c r="M77">
-        <v>310.83999999999997</v>
+        <v>232.68</v>
       </c>
       <c r="N77">
-        <v>0.31083999999999995</v>
+        <v>0.23268</v>
       </c>
       <c r="O77">
-        <v>10.6</v>
+        <v>334.31</v>
       </c>
       <c r="P77">
-        <v>13.170000000000002</v>
+        <v>10.16</v>
       </c>
       <c r="Q77" s="10">
         <v>46265</v>
       </c>
       <c r="R77" t="s">
-        <v>330</v>
+        <v>483</v>
       </c>
       <c r="S77" t="s">
         <v>30</v>
@@ -23795,58 +23795,58 @@
     </row>
     <row r="78" spans="1:20">
       <c r="A78">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>572</v>
+        <v>485</v>
       </c>
       <c r="C78" t="s">
-        <v>573</v>
+        <v>486</v>
       </c>
       <c r="D78" t="s">
-        <v>574</v>
+        <v>487</v>
       </c>
       <c r="E78" t="s">
-        <v>387</v>
+        <v>24</v>
       </c>
       <c r="F78" t="s">
-        <v>160</v>
+        <v>25</v>
       </c>
       <c r="G78" t="s">
-        <v>107</v>
+        <v>26</v>
       </c>
       <c r="H78" t="s">
-        <v>575</v>
+        <v>120</v>
       </c>
       <c r="I78" t="s">
-        <v>389</v>
+        <v>28</v>
       </c>
       <c r="J78">
-        <v>1890</v>
+        <v>1980</v>
       </c>
       <c r="K78">
-        <v>136</v>
+        <v>46</v>
       </c>
       <c r="L78">
-        <v>156875</v>
+        <v>31500</v>
       </c>
       <c r="M78">
-        <v>198.64</v>
+        <v>232.49</v>
       </c>
       <c r="N78">
-        <v>0.19863999999999998</v>
+        <v>0.23249</v>
       </c>
       <c r="O78">
-        <v>166.11</v>
+        <v>37.22</v>
       </c>
       <c r="P78">
-        <v>12.39</v>
+        <v>24.41</v>
       </c>
       <c r="Q78" s="10">
         <v>46265</v>
       </c>
       <c r="R78" t="s">
-        <v>576</v>
+        <v>488</v>
       </c>
       <c r="S78" t="s">
         <v>30</v>
@@ -23857,61 +23857,61 @@
     </row>
     <row r="79" spans="1:20">
       <c r="A79">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>596</v>
+        <v>490</v>
       </c>
       <c r="C79" t="s">
-        <v>597</v>
+        <v>491</v>
       </c>
       <c r="D79" t="s">
-        <v>598</v>
+        <v>492</v>
       </c>
       <c r="E79" t="s">
-        <v>379</v>
+        <v>24</v>
       </c>
       <c r="F79" t="s">
-        <v>160</v>
+        <v>25</v>
       </c>
       <c r="G79" t="s">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="H79" t="s">
-        <v>81</v>
+        <v>493</v>
       </c>
       <c r="I79" t="s">
-        <v>599</v>
+        <v>109</v>
       </c>
       <c r="J79">
-        <v>1924</v>
+        <v>2006</v>
       </c>
       <c r="K79">
-        <v>102</v>
+        <v>20</v>
       </c>
       <c r="L79">
-        <v>101513</v>
+        <v>125000</v>
       </c>
       <c r="M79">
-        <v>195.4</v>
+        <v>229.2</v>
       </c>
       <c r="N79">
-        <v>0.19540000000000002</v>
+        <v>0.22919999999999999</v>
       </c>
       <c r="O79">
-        <v>201</v>
+        <v>45.19</v>
       </c>
       <c r="P79">
-        <v>12.31</v>
+        <v>16.420000000000002</v>
       </c>
       <c r="Q79" s="10">
         <v>46265</v>
       </c>
       <c r="R79" t="s">
-        <v>593</v>
+        <v>494</v>
       </c>
       <c r="S79" t="s">
-        <v>600</v>
+        <v>30</v>
       </c>
       <c r="T79" t="s">
         <v>31</v>
@@ -23919,58 +23919,58 @@
     </row>
     <row r="80" spans="1:20">
       <c r="A80">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>420</v>
+        <v>496</v>
       </c>
       <c r="C80" t="s">
-        <v>421</v>
+        <v>497</v>
       </c>
       <c r="D80" t="s">
-        <v>422</v>
+        <v>498</v>
       </c>
       <c r="E80" t="s">
-        <v>270</v>
+        <v>24</v>
       </c>
       <c r="F80" t="s">
-        <v>160</v>
+        <v>25</v>
       </c>
       <c r="G80" t="s">
-        <v>236</v>
+        <v>26</v>
       </c>
       <c r="H80" t="s">
-        <v>423</v>
+        <v>27</v>
       </c>
       <c r="I80" t="s">
-        <v>271</v>
+        <v>28</v>
       </c>
       <c r="J80">
-        <v>1866</v>
+        <v>1975</v>
       </c>
       <c r="K80">
-        <v>160</v>
+        <v>51</v>
       </c>
       <c r="L80">
-        <v>271000</v>
+        <v>17200</v>
       </c>
       <c r="M80">
-        <v>250.88</v>
+        <v>229.12</v>
       </c>
       <c r="N80">
-        <v>0.25087999999999999</v>
+        <v>0.22912000000000002</v>
       </c>
       <c r="O80">
-        <v>110.73</v>
+        <v>13.09</v>
       </c>
       <c r="P80">
-        <v>11.96</v>
+        <v>41.11</v>
       </c>
       <c r="Q80" s="10">
         <v>46265</v>
       </c>
       <c r="R80" t="s">
-        <v>424</v>
+        <v>499</v>
       </c>
       <c r="S80" t="s">
         <v>30</v>
@@ -23981,58 +23981,58 @@
     </row>
     <row r="81" spans="1:20">
       <c r="A81">
-        <v>19</v>
+        <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>142</v>
+        <v>501</v>
       </c>
       <c r="C81" t="s">
-        <v>143</v>
+        <v>502</v>
       </c>
       <c r="D81" t="s">
-        <v>143</v>
+        <v>503</v>
       </c>
       <c r="E81" t="s">
-        <v>24</v>
+        <v>276</v>
       </c>
       <c r="F81" t="s">
-        <v>25</v>
+        <v>160</v>
       </c>
       <c r="G81" t="s">
-        <v>26</v>
+        <v>449</v>
       </c>
       <c r="H81" t="s">
-        <v>27</v>
+        <v>504</v>
       </c>
       <c r="I81" t="s">
         <v>28</v>
       </c>
       <c r="J81">
-        <v>1969</v>
+        <v>1879</v>
       </c>
       <c r="K81">
-        <v>57</v>
+        <v>147</v>
       </c>
       <c r="L81">
-        <v>31000</v>
+        <v>65177</v>
       </c>
       <c r="M81">
-        <v>764.34</v>
+        <v>225.3</v>
       </c>
       <c r="N81">
-        <v>0.76434000000000002</v>
+        <v>0.2253</v>
       </c>
       <c r="O81">
-        <v>37.450000000000003</v>
+        <v>34.65</v>
       </c>
       <c r="P81">
-        <v>11.95</v>
+        <v>26.170000000000005</v>
       </c>
       <c r="Q81" s="10">
         <v>46265</v>
       </c>
       <c r="R81" t="s">
-        <v>144</v>
+        <v>505</v>
       </c>
       <c r="S81" t="s">
         <v>30</v>
@@ -24043,16 +24043,16 @@
     </row>
     <row r="82" spans="1:20">
       <c r="A82">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>317</v>
+        <v>507</v>
       </c>
       <c r="C82" t="s">
-        <v>318</v>
+        <v>508</v>
       </c>
       <c r="D82" t="s">
-        <v>319</v>
+        <v>509</v>
       </c>
       <c r="E82" t="s">
         <v>24</v>
@@ -24061,40 +24061,40 @@
         <v>25</v>
       </c>
       <c r="G82" t="s">
-        <v>138</v>
+        <v>107</v>
       </c>
       <c r="H82" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="I82" t="s">
         <v>109</v>
       </c>
       <c r="J82">
-        <v>1978</v>
+        <v>1850</v>
       </c>
       <c r="K82">
-        <v>48</v>
+        <v>176</v>
       </c>
       <c r="L82">
-        <v>472400</v>
+        <v>76800</v>
       </c>
       <c r="M82">
-        <v>327.26</v>
+        <v>223.55</v>
       </c>
       <c r="N82">
-        <v>0.32726</v>
+        <v>0.22355</v>
       </c>
       <c r="O82">
-        <v>166.59</v>
+        <v>74.17</v>
       </c>
       <c r="P82">
-        <v>11.29</v>
+        <v>19.2</v>
       </c>
       <c r="Q82" s="10">
         <v>46265</v>
       </c>
       <c r="R82" t="s">
-        <v>320</v>
+        <v>510</v>
       </c>
       <c r="S82" t="s">
         <v>30</v>
@@ -24105,58 +24105,58 @@
     </row>
     <row r="83" spans="1:20">
       <c r="A83">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>415</v>
+        <v>512</v>
       </c>
       <c r="C83" t="s">
-        <v>416</v>
+        <v>513</v>
       </c>
       <c r="D83" t="s">
-        <v>417</v>
+        <v>513</v>
       </c>
       <c r="E83" t="s">
-        <v>276</v>
+        <v>24</v>
       </c>
       <c r="F83" t="s">
-        <v>160</v>
+        <v>25</v>
       </c>
       <c r="G83" t="s">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="H83" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="I83" t="s">
-        <v>277</v>
+        <v>109</v>
       </c>
       <c r="J83">
-        <v>1907</v>
+        <v>1911</v>
       </c>
       <c r="K83">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L83">
-        <v>85000</v>
+        <v>264300</v>
       </c>
       <c r="M83">
-        <v>251.71</v>
+        <v>221.32</v>
       </c>
       <c r="N83">
-        <v>0.25170999999999999</v>
+        <v>0.22131999999999999</v>
       </c>
       <c r="O83">
-        <v>267.33999999999997</v>
+        <v>68.91</v>
       </c>
       <c r="P83">
-        <v>11.26</v>
+        <v>15.310000000000002</v>
       </c>
       <c r="Q83" s="10">
         <v>46265</v>
       </c>
       <c r="R83" t="s">
-        <v>418</v>
+        <v>514</v>
       </c>
       <c r="S83" t="s">
         <v>30</v>
@@ -24167,16 +24167,16 @@
     </row>
     <row r="84" spans="1:20">
       <c r="A84">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="B84" t="s">
-        <v>152</v>
+        <v>524</v>
       </c>
       <c r="C84" t="s">
-        <v>153</v>
+        <v>525</v>
       </c>
       <c r="D84" t="s">
-        <v>154</v>
+        <v>526</v>
       </c>
       <c r="E84" t="s">
         <v>24</v>
@@ -24185,40 +24185,40 @@
         <v>25</v>
       </c>
       <c r="G84" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="H84" t="s">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="I84" t="s">
         <v>109</v>
       </c>
       <c r="J84">
-        <v>1870</v>
+        <v>1812</v>
       </c>
       <c r="K84">
-        <v>156</v>
+        <v>214</v>
       </c>
       <c r="L84">
-        <v>58000</v>
+        <v>226000</v>
       </c>
       <c r="M84">
-        <v>659.26</v>
+        <v>220.71</v>
       </c>
       <c r="N84">
-        <v>0.65925999999999996</v>
+        <v>0.22071000000000002</v>
       </c>
       <c r="O84">
-        <v>326</v>
+        <v>88.08</v>
       </c>
       <c r="P84">
-        <v>11.23</v>
+        <v>24.85</v>
       </c>
       <c r="Q84" s="10">
         <v>46265</v>
       </c>
       <c r="R84" t="s">
-        <v>155</v>
+        <v>527</v>
       </c>
       <c r="S84" t="s">
         <v>30</v>
@@ -24229,16 +24229,16 @@
     </row>
     <row r="85" spans="1:20">
       <c r="A85">
-        <v>35</v>
+        <v>88</v>
       </c>
       <c r="B85" t="s">
-        <v>228</v>
+        <v>537</v>
       </c>
       <c r="C85" t="s">
-        <v>229</v>
+        <v>538</v>
       </c>
       <c r="D85" t="s">
-        <v>230</v>
+        <v>539</v>
       </c>
       <c r="E85" t="s">
         <v>24</v>
@@ -24247,40 +24247,40 @@
         <v>25</v>
       </c>
       <c r="G85" t="s">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="H85" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="I85" t="s">
-        <v>109</v>
+        <v>28</v>
       </c>
       <c r="J85">
-        <v>1879</v>
+        <v>1988</v>
       </c>
       <c r="K85">
-        <v>147</v>
+        <v>38</v>
       </c>
       <c r="L85">
-        <v>43039</v>
+        <v>11100</v>
       </c>
       <c r="M85">
-        <v>403.25</v>
+        <v>215.08</v>
       </c>
       <c r="N85">
-        <v>0.40325</v>
+        <v>0.21508000000000002</v>
       </c>
       <c r="O85">
-        <v>185.88</v>
+        <v>13.18</v>
       </c>
       <c r="P85">
-        <v>10.46</v>
+        <v>39.06</v>
       </c>
       <c r="Q85" s="10">
         <v>46265</v>
       </c>
       <c r="R85" t="s">
-        <v>231</v>
+        <v>540</v>
       </c>
       <c r="S85" t="s">
         <v>30</v>
@@ -24291,58 +24291,58 @@
     </row>
     <row r="86" spans="1:20">
       <c r="A86">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="B86" t="s">
-        <v>480</v>
+        <v>542</v>
       </c>
       <c r="C86" t="s">
-        <v>481</v>
+        <v>543</v>
       </c>
       <c r="D86" t="s">
-        <v>482</v>
+        <v>544</v>
       </c>
       <c r="E86" t="s">
-        <v>405</v>
+        <v>24</v>
       </c>
       <c r="F86" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="G86" t="s">
-        <v>248</v>
+        <v>26</v>
       </c>
       <c r="H86" t="s">
-        <v>94</v>
+        <v>36</v>
       </c>
       <c r="I86" t="s">
-        <v>406</v>
+        <v>109</v>
       </c>
       <c r="J86">
-        <v>1937</v>
+        <v>1999</v>
       </c>
       <c r="K86">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="L86">
-        <v>390927</v>
+        <v>83334</v>
       </c>
       <c r="M86">
-        <v>232.68</v>
+        <v>213.84</v>
       </c>
       <c r="N86">
-        <v>0.23268</v>
+        <v>0.21384</v>
       </c>
       <c r="O86">
-        <v>334.31</v>
+        <v>42.82</v>
       </c>
       <c r="P86">
-        <v>10.16</v>
+        <v>23.97</v>
       </c>
       <c r="Q86" s="10">
         <v>46265</v>
       </c>
       <c r="R86" t="s">
-        <v>483</v>
+        <v>545</v>
       </c>
       <c r="S86" t="s">
         <v>30</v>
@@ -24353,58 +24353,58 @@
     </row>
     <row r="87" spans="1:20">
       <c r="A87">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="B87" t="s">
-        <v>367</v>
+        <v>547</v>
       </c>
       <c r="C87" t="s">
-        <v>368</v>
+        <v>548</v>
       </c>
       <c r="D87" t="s">
-        <v>368</v>
+        <v>549</v>
       </c>
       <c r="E87" t="s">
-        <v>24</v>
+        <v>550</v>
       </c>
       <c r="F87" t="s">
-        <v>25</v>
+        <v>160</v>
       </c>
       <c r="G87" t="s">
-        <v>289</v>
+        <v>107</v>
       </c>
       <c r="H87" t="s">
-        <v>290</v>
+        <v>126</v>
       </c>
       <c r="I87" t="s">
-        <v>109</v>
+        <v>551</v>
       </c>
       <c r="J87">
-        <v>2020</v>
+        <v>1857</v>
       </c>
       <c r="K87">
-        <v>6</v>
+        <v>169</v>
       </c>
       <c r="L87">
-        <v>180000</v>
+        <v>198403</v>
       </c>
       <c r="M87">
-        <v>281.39999999999998</v>
+        <v>211.82</v>
       </c>
       <c r="N87">
-        <v>0.28139999999999998</v>
+        <v>0.21181999999999998</v>
       </c>
       <c r="O87">
-        <v>90.37</v>
+        <v>69</v>
       </c>
       <c r="P87">
-        <v>9.85</v>
+        <v>32.270000000000003</v>
       </c>
       <c r="Q87" s="10">
         <v>46265</v>
       </c>
       <c r="R87" t="s">
-        <v>369</v>
+        <v>552</v>
       </c>
       <c r="S87" t="s">
         <v>30</v>
@@ -24415,58 +24415,58 @@
     </row>
     <row r="88" spans="1:20">
       <c r="A88">
-        <v>28</v>
+        <v>91</v>
       </c>
       <c r="B88" t="s">
-        <v>192</v>
+        <v>554</v>
       </c>
       <c r="C88" t="s">
-        <v>193</v>
+        <v>555</v>
       </c>
       <c r="D88" t="s">
-        <v>194</v>
+        <v>556</v>
       </c>
       <c r="E88" t="s">
-        <v>24</v>
+        <v>550</v>
       </c>
       <c r="F88" t="s">
-        <v>25</v>
+        <v>160</v>
       </c>
       <c r="G88" t="s">
-        <v>26</v>
+        <v>138</v>
       </c>
       <c r="H88" t="s">
-        <v>120</v>
+        <v>380</v>
       </c>
       <c r="I88" t="s">
-        <v>109</v>
+        <v>557</v>
       </c>
       <c r="J88">
-        <v>2013</v>
+        <v>1985</v>
       </c>
       <c r="K88">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="L88">
-        <v>57000</v>
+        <v>163000</v>
       </c>
       <c r="M88">
-        <v>455.42</v>
+        <v>210.73</v>
       </c>
       <c r="N88">
-        <v>0.45541999999999999</v>
+        <v>0.21073</v>
       </c>
       <c r="O88">
-        <v>62.81</v>
+        <v>42.5</v>
       </c>
       <c r="P88">
-        <v>9.51</v>
+        <v>20.92</v>
       </c>
       <c r="Q88" s="10">
         <v>46265</v>
       </c>
       <c r="R88" t="s">
-        <v>195</v>
+        <v>558</v>
       </c>
       <c r="S88" t="s">
         <v>30</v>
@@ -24477,16 +24477,16 @@
     </row>
     <row r="89" spans="1:20">
       <c r="A89">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="B89" t="s">
-        <v>332</v>
+        <v>560</v>
       </c>
       <c r="C89" t="s">
-        <v>333</v>
+        <v>561</v>
       </c>
       <c r="D89" t="s">
-        <v>334</v>
+        <v>562</v>
       </c>
       <c r="E89" t="s">
         <v>24</v>
@@ -24495,40 +24495,40 @@
         <v>25</v>
       </c>
       <c r="G89" t="s">
-        <v>26</v>
+        <v>532</v>
       </c>
       <c r="H89" t="s">
-        <v>66</v>
+        <v>533</v>
       </c>
       <c r="I89" t="s">
         <v>109</v>
       </c>
       <c r="J89">
-        <v>1984</v>
+        <v>2000</v>
       </c>
       <c r="K89">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="L89">
-        <v>97000</v>
+        <v>89900</v>
       </c>
       <c r="M89">
-        <v>300.17</v>
+        <v>208.51</v>
       </c>
       <c r="N89">
-        <v>0.30016999999999999</v>
+        <v>0.20851</v>
       </c>
       <c r="O89">
-        <v>134</v>
+        <v>139.13999999999999</v>
       </c>
       <c r="P89">
-        <v>8.75</v>
+        <v>16.510000000000002</v>
       </c>
       <c r="Q89" s="10">
         <v>46265</v>
       </c>
       <c r="R89" t="s">
-        <v>335</v>
+        <v>563</v>
       </c>
       <c r="S89" t="s">
         <v>30</v>
@@ -24539,58 +24539,58 @@
     </row>
     <row r="90" spans="1:20">
       <c r="A90">
-        <v>11</v>
+        <v>93</v>
       </c>
       <c r="B90" t="s">
-        <v>91</v>
+        <v>565</v>
       </c>
       <c r="C90" t="s">
-        <v>92</v>
+        <v>566</v>
       </c>
       <c r="D90" t="s">
-        <v>93</v>
+        <v>567</v>
       </c>
       <c r="E90" t="s">
-        <v>24</v>
+        <v>568</v>
       </c>
       <c r="F90" t="s">
-        <v>25</v>
+        <v>160</v>
       </c>
       <c r="G90" t="s">
         <v>26</v>
       </c>
       <c r="H90" t="s">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="I90" t="s">
-        <v>28</v>
+        <v>569</v>
       </c>
       <c r="J90">
-        <v>2003</v>
+        <v>1923</v>
       </c>
       <c r="K90">
-        <v>23</v>
+        <v>103</v>
       </c>
       <c r="L90">
-        <v>134785</v>
+        <v>69505</v>
       </c>
       <c r="M90">
-        <v>1448</v>
+        <v>200.31</v>
       </c>
       <c r="N90">
-        <v>1.448</v>
+        <v>0.20031000000000002</v>
       </c>
       <c r="O90">
-        <v>97.87</v>
+        <v>51.37</v>
       </c>
       <c r="P90">
-        <v>5.9</v>
+        <v>42.23</v>
       </c>
       <c r="Q90" s="10">
         <v>46265</v>
       </c>
       <c r="R90" t="s">
-        <v>95</v>
+        <v>570</v>
       </c>
       <c r="S90" t="s">
         <v>30</v>
@@ -24601,58 +24601,58 @@
     </row>
     <row r="91" spans="1:20">
       <c r="A91">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="B91" t="s">
-        <v>135</v>
+        <v>572</v>
       </c>
       <c r="C91" t="s">
+        <v>573</v>
+      </c>
+      <c r="D91" t="s">
+        <v>574</v>
+      </c>
+      <c r="E91" t="s">
+        <v>387</v>
+      </c>
+      <c r="F91" t="s">
+        <v>160</v>
+      </c>
+      <c r="G91" t="s">
+        <v>107</v>
+      </c>
+      <c r="H91" t="s">
+        <v>575</v>
+      </c>
+      <c r="I91" t="s">
+        <v>389</v>
+      </c>
+      <c r="J91">
+        <v>1890</v>
+      </c>
+      <c r="K91">
         <v>136</v>
       </c>
-      <c r="D91" t="s">
-        <v>137</v>
-      </c>
-      <c r="E91" t="s">
-        <v>24</v>
-      </c>
-      <c r="F91" t="s">
-        <v>25</v>
-      </c>
-      <c r="G91" t="s">
-        <v>138</v>
-      </c>
-      <c r="H91" t="s">
-        <v>139</v>
-      </c>
-      <c r="I91" t="s">
-        <v>28</v>
-      </c>
-      <c r="J91">
-        <v>1962</v>
-      </c>
-      <c r="K91">
-        <v>64</v>
-      </c>
       <c r="L91">
-        <v>2100000</v>
+        <v>156875</v>
       </c>
       <c r="M91">
-        <v>835.12</v>
+        <v>198.64</v>
       </c>
       <c r="N91">
-        <v>0.83511999999999997</v>
+        <v>0.19863999999999998</v>
       </c>
       <c r="O91">
-        <v>725.3</v>
+        <v>166.11</v>
       </c>
       <c r="P91">
-        <v>4.13</v>
+        <v>12.39</v>
       </c>
       <c r="Q91" s="10">
         <v>46265</v>
       </c>
       <c r="R91" t="s">
-        <v>140</v>
+        <v>576</v>
       </c>
       <c r="S91" t="s">
         <v>30</v>
@@ -24663,58 +24663,58 @@
     </row>
     <row r="92" spans="1:20">
       <c r="A92">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="B92" t="s">
-        <v>223</v>
+        <v>578</v>
       </c>
       <c r="C92" t="s">
-        <v>224</v>
+        <v>579</v>
       </c>
       <c r="D92" t="s">
-        <v>225</v>
+        <v>580</v>
       </c>
       <c r="E92" t="s">
-        <v>24</v>
+        <v>363</v>
       </c>
       <c r="F92" t="s">
         <v>25</v>
       </c>
       <c r="G92" t="s">
-        <v>138</v>
+        <v>107</v>
       </c>
       <c r="H92" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="I92" t="s">
-        <v>28</v>
+        <v>364</v>
       </c>
       <c r="J92">
-        <v>1983</v>
+        <v>1855</v>
       </c>
       <c r="K92">
-        <v>43</v>
+        <v>171</v>
       </c>
       <c r="L92">
-        <v>341000</v>
+        <v>94867</v>
       </c>
       <c r="M92">
-        <v>418.36</v>
+        <v>198.02</v>
       </c>
       <c r="N92">
-        <v>0.41836000000000001</v>
+        <v>0.19802</v>
       </c>
       <c r="O92">
-        <v>293.58</v>
+        <v>46.37</v>
       </c>
       <c r="P92">
-        <v>3.93</v>
+        <v>29.100000000000005</v>
       </c>
       <c r="Q92" s="10">
         <v>46265</v>
       </c>
       <c r="R92" t="s">
-        <v>226</v>
+        <v>581</v>
       </c>
       <c r="S92" t="s">
         <v>30</v>
@@ -24725,58 +24725,58 @@
     </row>
     <row r="93" spans="1:20">
       <c r="A93">
-        <v>44</v>
+        <v>96</v>
       </c>
       <c r="B93" t="s">
-        <v>280</v>
+        <v>583</v>
       </c>
       <c r="C93" t="s">
-        <v>281</v>
+        <v>584</v>
       </c>
       <c r="D93" t="s">
-        <v>282</v>
+        <v>585</v>
       </c>
       <c r="E93" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="F93" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="G93" t="s">
-        <v>107</v>
+        <v>26</v>
       </c>
       <c r="H93" t="s">
-        <v>283</v>
+        <v>27</v>
       </c>
       <c r="I93" t="s">
-        <v>109</v>
+        <v>586</v>
       </c>
       <c r="J93">
-        <v>1977</v>
+        <v>1997</v>
       </c>
       <c r="K93">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="L93">
-        <v>390000</v>
+        <v>0</v>
       </c>
       <c r="M93">
-        <v>349.97</v>
+        <v>197.85</v>
       </c>
       <c r="N93">
-        <v>0.34997</v>
+        <v>0.19785</v>
       </c>
       <c r="O93">
-        <v>449.71</v>
+        <v>19.23</v>
       </c>
       <c r="P93">
-        <v>3.2300000000000004</v>
+        <v>20.95</v>
       </c>
       <c r="Q93" s="10">
         <v>46265</v>
       </c>
       <c r="R93" t="s">
-        <v>284</v>
+        <v>587</v>
       </c>
       <c r="S93" t="s">
         <v>30</v>
@@ -24787,16 +24787,16 @@
     </row>
     <row r="94" spans="1:20">
       <c r="A94">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="B94" t="s">
-        <v>187</v>
+        <v>589</v>
       </c>
       <c r="C94" t="s">
-        <v>188</v>
+        <v>590</v>
       </c>
       <c r="D94" t="s">
-        <v>189</v>
+        <v>591</v>
       </c>
       <c r="E94" t="s">
         <v>24</v>
@@ -24808,40 +24808,40 @@
         <v>26</v>
       </c>
       <c r="H94" t="s">
-        <v>27</v>
+        <v>592</v>
       </c>
       <c r="I94" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="J94">
-        <v>1968</v>
+        <v>1932</v>
       </c>
       <c r="K94">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="L94">
-        <v>85100</v>
+        <v>170000</v>
       </c>
       <c r="M94">
-        <v>472.57</v>
+        <v>196.62</v>
       </c>
       <c r="N94">
-        <v>0.47256999999999999</v>
+        <v>0.19662000000000002</v>
       </c>
       <c r="O94">
-        <v>53.76</v>
+        <v>23.1</v>
       </c>
       <c r="P94">
-        <v>2.94</v>
+        <v>24.25</v>
       </c>
       <c r="Q94" s="10">
         <v>46265</v>
       </c>
       <c r="R94" t="s">
-        <v>190</v>
+        <v>593</v>
       </c>
       <c r="S94" t="s">
-        <v>30</v>
+        <v>594</v>
       </c>
       <c r="T94" t="s">
         <v>31</v>
@@ -24849,61 +24849,61 @@
     </row>
     <row r="95" spans="1:20">
       <c r="A95">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="B95" t="s">
-        <v>475</v>
+        <v>596</v>
       </c>
       <c r="C95" t="s">
-        <v>476</v>
+        <v>597</v>
       </c>
       <c r="D95" t="s">
-        <v>477</v>
+        <v>598</v>
       </c>
       <c r="E95" t="s">
-        <v>24</v>
+        <v>379</v>
       </c>
       <c r="F95" t="s">
-        <v>25</v>
+        <v>160</v>
       </c>
       <c r="G95" t="s">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="H95" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="I95" t="s">
-        <v>28</v>
+        <v>599</v>
       </c>
       <c r="J95">
-        <v>2011</v>
+        <v>1924</v>
       </c>
       <c r="K95">
-        <v>15</v>
+        <v>102</v>
       </c>
       <c r="L95">
-        <v>10698</v>
+        <v>101513</v>
       </c>
       <c r="M95">
-        <v>236.01</v>
+        <v>195.4</v>
       </c>
       <c r="N95">
-        <v>0.23601</v>
+        <v>0.19540000000000002</v>
       </c>
       <c r="O95">
-        <v>5.09</v>
+        <v>201</v>
       </c>
       <c r="P95">
-        <v>0.03</v>
+        <v>12.31</v>
       </c>
       <c r="Q95" s="10">
         <v>46265</v>
       </c>
       <c r="R95" t="s">
-        <v>478</v>
+        <v>593</v>
       </c>
       <c r="S95" t="s">
-        <v>30</v>
+        <v>600</v>
       </c>
       <c r="T95" t="s">
         <v>31</v>
@@ -24911,16 +24911,16 @@
     </row>
     <row r="96" spans="1:20">
       <c r="A96">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="B96" t="s">
-        <v>63</v>
+        <v>608</v>
       </c>
       <c r="C96" t="s">
-        <v>64</v>
+        <v>609</v>
       </c>
       <c r="D96" t="s">
-        <v>65</v>
+        <v>610</v>
       </c>
       <c r="E96" t="s">
         <v>24</v>
@@ -24929,43 +24929,43 @@
         <v>25</v>
       </c>
       <c r="G96" t="s">
-        <v>26</v>
+        <v>532</v>
       </c>
       <c r="H96" t="s">
-        <v>66</v>
+        <v>533</v>
       </c>
       <c r="I96" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="J96">
-        <v>2002</v>
+        <v>1994</v>
       </c>
       <c r="K96">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L96">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="M96">
-        <v>1876</v>
+        <v>194.29</v>
       </c>
       <c r="N96">
-        <v>1.8759999999999999</v>
+        <v>0.19428999999999999</v>
       </c>
       <c r="O96">
-        <v>8.76</v>
+        <v>88.308999999999997</v>
       </c>
       <c r="P96">
-        <v>-22.59</v>
+        <v>16.170000000000002</v>
       </c>
       <c r="Q96" s="10">
         <v>46265</v>
       </c>
       <c r="R96" t="s">
-        <v>68</v>
+        <v>593</v>
       </c>
       <c r="S96" t="s">
-        <v>30</v>
+        <v>611</v>
       </c>
       <c r="T96" t="s">
         <v>31</v>
